--- a/docs/03_詳細設計/04_クラス・内部IF設計/KF-DD-CLS-06_通知_クラス詳細設計書.xlsx
+++ b/docs/03_詳細設計/04_クラス・内部IF設計/KF-DD-CLS-06_通知_クラス詳細設計書.xlsx
@@ -689,7 +689,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.2</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
     <row r="16">
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：22 本のオンライン詳細設計書（ONL-001〜022）と 3 本のバッチ詳細設計書（BAT-001〜003）の規格 JSON をクラス単位に集約・再構成したもの。同一クラスのメソッドを複数 ONL / BAT が定義・追記している場合は統合し、重複を除いた。v2.0 で解消した食い違いと、なお残る食い違いは 4. に整理した。</t>
+          <t>本書の位置づけ：23 本のオンライン詳細設計書（ONL-001〜023）と 3 本のバッチ詳細設計書（BAT-001〜003）の規格 JSON、および実コードから起こした API-024〜026（ONL-024〜026。休憩・離席の打刻、部署一覧。専用の ONL 詳細設計書は未作成）を、クラス単位に集約・再構成したもの。同一クラスのメソッドを複数 ONL / BAT が定義・追記している場合は統合し、重複を除いた。解消した食い違いと、なお残る食い違い（実コード照合の結果を含む）は 4. に整理した。</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>record 宣言のコンポーネント（ONL-019 の宣言）</t>
+          <t>record 宣言のコンポーネント（実コード dto/NotificationListResponse.java）</t>
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
@@ -1363,12 +1363,12 @@
       <c r="B42" s="4" t="inlineStr">
         <is>
           <t>return new NotificationResponse(
-    n.getId(),
-    n.getType(),                          // 旧データは null
-    n.getMessage(),
-    n.getRequestId(),                     // LEAVE_* は null（JSON に null で出力）
-    AppTime.toIso(n.getCreatedAt()),     // 2026-10-02T17:30:00+09:00
-    n.isRead());</t>
+        n.getId(),
+        n.getType(),
+        n.getMessage(),
+        n.getRequestId(),
+        n.getCreatedAt() == null ? null : AppTime.toIso(n.getCreatedAt()),
+        n.isRead());</t>
         </is>
       </c>
       <c r="C42" s="8" t="n"/>
@@ -1827,7 +1827,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>record 宣言のコンポーネント（ONL-019 の宣言）</t>
+          <t>record 宣言のコンポーネント（実コード dto/NotificationResponse.java）</t>
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>@JsonProperty("isRead")</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D31" s="8" t="n"/>
@@ -2421,12 +2421,12 @@
       <c r="B56" s="15" t="inlineStr">
         <is>
           <t>return new NotificationResponse(
-    n.getId(),
-    n.getType(),                          // 旧データは null
-    n.getMessage(),
-    n.getRequestId(),                     // LEAVE_* は null（JSON に null で出力）
-    AppTime.toIso(n.getCreatedAt()),     // 2026-10-02T17:30:00+09:00
-    n.isRead());</t>
+        n.getId(),
+        n.getType(),
+        n.getMessage(),
+        n.getRequestId(),
+        n.getCreatedAt() == null ? null : AppTime.toIso(n.getCreatedAt()),
+        n.isRead());</t>
         </is>
       </c>
       <c r="C56" s="8" t="n"/>
@@ -2611,12 +2611,12 @@
       <c r="B70" s="4" t="inlineStr">
         <is>
           <t>return new NotificationResponse(
-    n.getId(),
-    n.getType(),                          // 旧データは null
-    n.getMessage(),
-    n.getRequestId(),                     // LEAVE_* は null（JSON に null で出力）
-    AppTime.toIso(n.getCreatedAt()),     // 2026-10-02T17:30:00+09:00
-    n.isRead());</t>
+        n.getId(),
+        n.getType(),
+        n.getMessage(),
+        n.getRequestId(),
+        n.getCreatedAt() == null ? null : AppTime.toIso(n.getCreatedAt()),
+        n.isRead());</t>
         </is>
       </c>
       <c r="C70" s="8" t="n"/>
@@ -2750,7 +2750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F13"/>
+  <dimension ref="A2:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2764,7 +2764,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>4.1 解消済み（v2.0）：更新済み規格で是正された食い違い（前版の報告分。規格 JSON を機械照合して確認）</t>
+          <t>4.1 解消済み：規格の更新・実装反映で是正された食い違い（前版までの報告分。規格 JSON と実コードを照合して確認）</t>
         </is>
       </c>
       <c r="B2" s="8" t="n"/>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>v2.0 の状態</t>
+          <t>現在の状態</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>解消済み（v2.0）</t>
+          <t>解消済み</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>解消済み（v2.0）</t>
+          <t>解消済み</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>解消済み（v2.0）</t>
+          <t>解消済み</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>解消済み（v2.0）</t>
+          <t>解消済み</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -2925,144 +2925,174 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>4.2 未決事項・残る食い違い（v2.0 の検証で新たに見つかったもの／外部文書の課題）</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="9" t="n"/>
-    </row>
-    <row r="10" ht="19" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="8" ht="64" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>解消済み</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>NotificationService#existsMonthly の統一（BAT-002 ↔ ONL-019）</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>ONL-019 と BAT-002 が別シグネチャ・別の重複判定キーを定義していた</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>ONL-019 が 3 引数版と本文先頭キー付き 4 引数版 existsMonthly(userId, type, keyPrefix, yearMonth) を定義し、BAT-002 は 4 引数版を使用。実コードの NotificationService / NotificationRepository にも両方ある</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>ONL-019, BAT-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="49" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>解消済み</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>通知 type の定数化（BAT-001/002 ↔ ONL-005）</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>BAT が文字列リテラル LEAVE_GRANT / MANDATORY_LEAVE_ALERT を使い、notifications.type が保存されない前提だった</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>NotificationType.LEAVE_GRANTED / LEAVE_ALERT を使用。notifications.type・request_id は保存される（V1__init_schema.sql に列と FK がある）</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>ONL-005, BAT-001, BAT-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>4.2 未決事項・残る食い違い（実コード照合で確認した設計↔実装の差異／規格間の差異／外部文書の課題）</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="9" t="n"/>
+    </row>
+    <row r="12" ht="19" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>詳細（記述の食い違い）</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>統一方針・対応</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>関連 ONL / BAT</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="124" customHeight="1">
-      <c r="A11" s="4" t="n">
+    <row r="13" ht="64" customHeight="1">
+      <c r="A13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>例外</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>NotificationRepository#existsByUserIdAndTypeAndMessageStartingWithAndCreatedAtGreaterThanEqualAndCreatedAtLessThan の例外記述が ONL 間で異なる（一方は「なし」）</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>ONL-019: なし；BAT-002: DataAccessException</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>具体的に記述している側を採用（実行時例外 PessimisticLockingFailureException 等は共通で E-012）</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>ONL-019, BAT-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="124" customHeight="1">
+      <c r="A14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>notifications.is_read のフィールド名・型が ONL / BAT 間で異なる</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>ONL-005: read / boolean / NULL 不可；ONL-008: read / boolean / NULL 不可；ONL-010: read / boolean / NULL 不可；ONL-011: read / boolean / NULL 不可；ONL-012: read / boolean / NULL 不可；ONL-017: read / boolean / NULL 不可；ONL-019: read / boolean / NULL 不可；ONL-022: read / boolean / NULL 不可；BAT-001: isRead / Boolean / NULL 不可；BAT-002: read / boolean / NULL 不可</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>定義元 ONL の表記に統一（ONL-019 の Notification：フィールド read、boolean、getter isRead()）。BAT-001 / BAT-002 のマッピング表の修正が必要</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>ONL-005, ONL-008, ONL-010, ONL-011, ONL-012, ONL-017, ONL-019, ONL-022, BAT-001, BAT-002</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="139" customHeight="1">
-      <c r="A12" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>BAT↔ONL</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>NotificationService#existsMonthly が ONL-019 と BAT-002 で別シグネチャ（重複判定のキーも異なる）</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>ONL-019: existsMonthly(Long userId, String type, YearMonth yearMonth)＝type と月で判定（NotificationRepository#existsByUserIdAndTypeAndCreatedAtGreaterThanEqualAndCreatedAtLessThan）。BAT-002: existsMonthly(Long userId, String likePattern, LocalDateTime from, LocalDateTime to)＋NotificationRepository#existsMonthlyByPattern＝本文の前方一致（selfPrefix / adminPrefix）で判定。BAT-002 は『ONL-019 は一覧取得・既読化のみ定義』と記載しており ONL-019 の現状と食い違う。</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>type が保存される（ONL-005 D-16）ため、本人宛て／管理者宛てを type で区別できるなら ONL-019 版に統一。区別できないなら BAT-002 版を別名（例 existsMonthlyByMessagePrefix）にして併存。規格改訂が必要</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>ONL-019, BAT-002</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="94" customHeight="1">
-      <c r="A13" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>BAT↔ONL</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>BAT の通知 type 値が NotificationType 定数と不一致で、保存有無の記述も古い</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>BAT-001 は notify(userId, "LEAVE_GRANT", …)、BAT-002 は "MANDATORY_LEAVE_ALERT" を渡す。ONL-005 の NotificationType は LEAVE_GRANTED / LEAVE_ALERT（7 値）。また BAT-001 D-13・BAT-002 は『notifications に type / request_id 列が無く保存されない』と記載するが、ONL-005 D-16 は保存に変更済み。</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>NotificationType.LEAVE_GRANTED / LEAVE_ALERT の定数を使用（文字列リテラルを使わない）。BAT-001 / BAT-002 の記述（D-13 ほか）を『保存される』に改訂</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>ONL-005, BAT-001, BAT-002</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A11:F11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3075,7 +3105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3157,6 +3187,52 @@
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4" ht="79" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>実コードとの全面照合（コードが唯一の正）：メソッドの処理（疑似コード）を実コードの本体に置換（コードと乖離していたもの）、シグネチャ（引数名・修飾子）・コンストラクタ依存・Repository のクエリ記述を実装に合わせて訂正。該当クラスのトークン無効化・INACTIVE の扱いの記述を ActiveUserFilter 実装後の内容に更新</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="64" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>実コード再照合（2026/10/05 夜）：本領域のクラスに変更なし。他領域の追加（API-024〜026 ほか）に伴い、依存関係・クラス構成図のみ再生成。BREAK_CORRECTION の通知文言は RequestService / ApprovalService 側（領域 03 / 04）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4406,7 +4482,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>使用メソッドは ONL の疑似コード中の呼出しから抽出（実装時はコンストラクタ引数として宣言する）。</t>
+          <t>コンストラクタ引数は実コードのとおり。使用メソッドは各メソッドの処理（実コード）中の参照から抽出。</t>
         </is>
       </c>
       <c r="C31" s="8" t="n"/>
@@ -4474,7 +4550,7 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>public NotificationListResponse list(Jwt jwt)</t>
+          <t>public NotificationListResponse list(Authentication auth)</t>
         </is>
       </c>
       <c r="C36" s="9" t="n"/>
@@ -4502,7 +4578,7 @@
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>public NotificationResponse markAsRead( Long id, Jwt jwt)</t>
+          <t>public NotificationResponse markAsRead( Long id, Authentication auth)</t>
         </is>
       </c>
       <c r="C37" s="9" t="n"/>
@@ -4570,7 +4646,7 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>public NotificationListResponse list(@AuthenticationPrincipal Jwt jwt)</t>
+          <t>public NotificationListResponse list(Authentication auth)</t>
         </is>
       </c>
       <c r="C41" s="8" t="n"/>
@@ -4634,17 +4710,17 @@
     <row r="45" ht="19" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>jwt</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Jwt</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>認証済みトークン。sub = users.id</t>
+          <t>認証情報（Spring Security が注入）。getName() = users.id（JWT の sub）</t>
         </is>
       </c>
       <c r="D45" s="8" t="n"/>
@@ -4707,7 +4783,7 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>1. Long userId = Long.valueOf(jwt.getSubject());
+          <t>1. Long userId = Long.valueOf(auth.getName());
 2. return notificationService.getNotifications(userId);</t>
         </is>
       </c>
@@ -4816,7 +4892,7 @@
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>public NotificationResponse markAsRead( @PathVariable("id") Long id, @AuthenticationPrincipal Jwt jwt)</t>
+          <t>public NotificationResponse markAsRead( @PathVariable("id") Long id, Authentication auth)</t>
         </is>
       </c>
       <c r="C56" s="8" t="n"/>
@@ -4899,17 +4975,17 @@
     <row r="61" ht="19" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>jwt</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Jwt</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>認証済みトークン。sub = users.id</t>
+          <t>認証情報（Spring Security が注入）。getName() = users.id（JWT の sub）</t>
         </is>
       </c>
       <c r="D61" s="8" t="n"/>
@@ -4973,7 +5049,7 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>1. Long userId = Long.valueOf(jwt.getSubject());
+          <t>1. Long userId = Long.valueOf(auth.getName());
 2. return notificationService.markAsRead(userId, id);</t>
         </is>
       </c>
@@ -5039,7 +5115,7 @@
       <c r="B69" s="4" t="inlineStr">
         <is>
           <t>リクエストボディは受け取らない。
-id が数値に変換できない場合は MethodArgumentTypeMismatchException となり、GlobalExceptionHandler#handleTypeMismatch が 400 / E-002 に変換する（ONL-001 の共通基盤への追加改修で定義済み。本処理では追加しない）。</t>
+id が数値に変換できない場合は MethodArgumentTypeMismatchException となり、GlobalExceptionHandler#handleBadParameter が 400 / E-002 に変換する（ONL-001 の共通基盤への追加改修で定義済み。本処理では追加しない）。</t>
         </is>
       </c>
       <c r="C69" s="8" t="n"/>
@@ -5314,7 +5390,7 @@
       <c r="D84" s="9" t="n"/>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>400 E-002「入力内容が正しくありません。」（handleTypeMismatch）。500 / E-012 にならない</t>
+          <t>400 E-002「入力内容が正しくありません。」（handleBadParameter）。500 / E-012 にならない</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -5916,7 +5992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F209"/>
+  <dimension ref="A1:F189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6194,7 +6270,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>ApprovalService、LeaveBalanceService、LeaveGrantUnitService、MandatoryLeaveAlertUnitService、MandatoryLeaveMessages、NotificationController、RequestService</t>
+          <t>ApprovalService、LeaveBalanceService、LeaveGrantUnitService、MandatoryLeaveAlertUnitService、MandatoryLeaveMessages、NotificationController、NotificationRepository、RequestService</t>
         </is>
       </c>
       <c r="C19" s="8" t="n"/>
@@ -6570,7 +6646,7 @@
       </c>
       <c r="F35" s="9" t="n"/>
     </row>
-    <row r="36" ht="34" customHeight="1">
+    <row r="36" ht="49" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
           <t>notificationRepository</t>
@@ -6583,7 +6659,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>markAsRead, notify</t>
+          <t>existsMonthly, existsMonthly（4引数 overload）/ existsBy…MessageStartingWith…, getNotifications, markAsRead, notify</t>
         </is>
       </c>
       <c r="D36" s="9" t="n"/>
@@ -6602,7 +6678,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>使用メソッドは ONL の疑似コード中の呼出しから抽出（実装時はコンストラクタ引数として宣言する）。</t>
+          <t>コンストラクタ引数は実コードのとおり。使用メソッドは各メソッドの処理（実コード）中の参照から抽出。</t>
         </is>
       </c>
       <c r="C37" s="8" t="n"/>
@@ -6662,15 +6738,15 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="79" customHeight="1">
+    <row r="42" ht="34" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>1. existsByUserIdAndTypeAndMessageStartingWithAndCreatedAtGreaterThanEqualAndCreatedAtLessThan</t>
+          <t>1. existsMonthly</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>boolean existsByUserIdAndTypeAndMessageStartingWithAndCreatedAtGreaterThanEqualAndCreatedAtLessThan( Long userId, String type, String messagePrefix, LocalDateTime from, LocalDateTime to)</t>
+          <t>public boolean existsMonthly(Long userId, String type, String keyPrefix, YearMonth yearMonth)</t>
         </is>
       </c>
       <c r="C42" s="9" t="n"/>
@@ -6681,7 +6757,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>BAT-002</t>
+          <t>BAT-002, ONL-019</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -6693,74 +6769,74 @@
     <row r="43" ht="49" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2. existsMonthly</t>
+          <t>2. notify</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>public boolean existsMonthly(Long userId, String type, String keyPrefix, YearMonth yearMonth)</t>
+          <t>public void notify(Long userId, String type, String message, Long requestId)</t>
         </is>
       </c>
       <c r="C43" s="9" t="n"/>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>void</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>BAT-002, ONL-019</t>
+          <t>ONL-005</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Service（BAT-002 の求めで ONL-019 が追加する overload。3 引数版も残す）</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="49" customHeight="1">
+          <t>Service（新規・共有。全 ONL の通知登録の唯一の入口。疑似コードの定義元は本書）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="34" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>3. notify</t>
+          <t>3. getNotifications</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>public void notify(Long userId, String type, String message, Long requestId)</t>
+          <t>public NotificationListResponse getNotifications(Long userId)</t>
         </is>
       </c>
       <c r="C44" s="9" t="n"/>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>void</t>
+          <t>NotificationListResponse</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>ONL-005</t>
+          <t>ONL-019</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Service（新規・共有。全 ONL の通知登録の唯一の入口。疑似コードの定義元は本書）</t>
+          <t>Service（ONL-019 一覧）</t>
         </is>
       </c>
     </row>
     <row r="45" ht="34" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>4. getNotifications</t>
+          <t>4. markAsRead</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>public NotificationListResponse getNotifications(Long userId)</t>
+          <t>public NotificationResponse markAsRead(Long userId, Long notificationId)</t>
         </is>
       </c>
       <c r="C45" s="9" t="n"/>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>NotificationListResponse</t>
+          <t>NotificationResponse</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -6770,25 +6846,25 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Service（ONL-019 一覧）</t>
+          <t>Service（ONL-019 既読化）</t>
         </is>
       </c>
     </row>
     <row r="46" ht="34" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>5. markAsRead</t>
+          <t>5. existsMonthly</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>public NotificationResponse markAsRead(Long userId, Long notificationId)</t>
+          <t>public boolean existsMonthly(Long userId, String type, YearMonth yearMonth)</t>
         </is>
       </c>
       <c r="C46" s="9" t="n"/>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>NotificationResponse</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -6798,42 +6874,26 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Service（ONL-019 既読化）</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="34" customHeight="1">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>6. existsMonthly</t>
-        </is>
-      </c>
-      <c r="B47" s="13" t="inlineStr">
-        <is>
-          <t>public boolean existsMonthly(Long userId, String type, YearMonth yearMonth)</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="n"/>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>ONL-019</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
           <t>Service（ONL-019 が追加。バッチの月次重複防止用）</t>
         </is>
       </c>
     </row>
+    <row r="47" ht="19" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>③-2 メソッド詳細</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n"/>
+      <c r="C47" s="8" t="n"/>
+      <c r="D47" s="8" t="n"/>
+      <c r="E47" s="8" t="n"/>
+      <c r="F47" s="9" t="n"/>
+    </row>
     <row r="48" ht="19" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>③-2 メソッド詳細</t>
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>③-2-1  NotificationService#existsMonthly  （一覧 No. 1）</t>
         </is>
       </c>
       <c r="B48" s="8" t="n"/>
@@ -6843,26 +6903,31 @@
       <c r="F48" s="9" t="n"/>
     </row>
     <row r="49" ht="19" customHeight="1">
-      <c r="A49" s="14" t="inlineStr">
-        <is>
-          <t>③-2-1  NotificationService#existsByUserIdAndTypeAndMessageStartingWithAndCreatedAtGreaterThanEqualAndCreatedAtLessThan  （一覧 No. 1）</t>
-        </is>
-      </c>
-      <c r="B49" s="8" t="n"/>
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Service ＋ Repository（本書で ONL-019 に追加）</t>
+        </is>
+      </c>
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="9" t="n"/>
     </row>
-    <row r="50" ht="19" customHeight="1">
+    <row r="50" ht="34" customHeight="1">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>種別</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>Service ＋ Repository（本書で ONL-019 に追加）</t>
+          <t>シグネチャ</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>@Transactional(readOnly = true)
+public boolean existsMonthly(Long userId, String type, String keyPrefix, YearMonth yearMonth)</t>
         </is>
       </c>
       <c r="C50" s="8" t="n"/>
@@ -6873,12 +6938,12 @@
     <row r="51" ht="34" customHeight="1">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>シグネチャ</t>
-        </is>
-      </c>
-      <c r="B51" s="15" t="inlineStr">
-        <is>
-          <t>boolean existsByUserIdAndTypeAndMessageStartingWithAndCreatedAtGreaterThanEqualAndCreatedAtLessThan( Long userId, String type, String messagePrefix, LocalDateTime from, LocalDateTime to)</t>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>指定ユーザー・指定種別の通知のうち、本文が keyPrefix で始まるもの（対象者・付与日が同じもの）が、指定した年月（JST）に既に作成されているかを返す。</t>
         </is>
       </c>
       <c r="C51" s="8" t="n"/>
@@ -6886,15 +6951,15 @@
       <c r="E51" s="8" t="n"/>
       <c r="F51" s="9" t="n"/>
     </row>
-    <row r="52" ht="34" customHeight="1">
+    <row r="52" ht="19" customHeight="1">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>説明</t>
+          <t>アノテーション</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>指定ユーザー・指定種別の通知のうち、本文が keyPrefix で始まるもの（対象者・付与日が同じもの）が、指定した年月（JST）に既に作成されているかを返す。</t>
+          <t>@Transactional(readOnly = true)（Service）</t>
         </is>
       </c>
       <c r="C52" s="8" t="n"/>
@@ -6903,35 +6968,39 @@
       <c r="F52" s="9" t="n"/>
     </row>
     <row r="53" ht="19" customHeight="1">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>アノテーション</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>@Transactional(readOnly = true)（Service）</t>
-        </is>
-      </c>
-      <c r="C53" s="8" t="n"/>
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>引数名</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
       <c r="D53" s="8" t="n"/>
       <c r="E53" s="8" t="n"/>
       <c r="F53" s="9" t="n"/>
     </row>
     <row r="54" ht="19" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>引数名</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>説明</t>
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>userId</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>宛先</t>
         </is>
       </c>
       <c r="D54" s="8" t="n"/>
@@ -6941,17 +7010,17 @@
     <row r="55" ht="19" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>userId</t>
+          <t>type</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>宛先</t>
+          <t>通知種別（BAT-002 は NotificationType.LEAVE_ALERT）</t>
         </is>
       </c>
       <c r="D55" s="8" t="n"/>
@@ -6961,7 +7030,7 @@
     <row r="56" ht="19" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>keyPrefix</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -6971,7 +7040,7 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>通知種別（BAT-002 は NotificationType.LEAVE_ALERT）</t>
+          <t>本文の先頭キー（MandatoryLeaveMessages.key の戻り値。ワイルドカード不要）</t>
         </is>
       </c>
       <c r="D56" s="8" t="n"/>
@@ -6981,17 +7050,17 @@
     <row r="57" ht="19" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>keyPrefix</t>
+          <t>yearMonth</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>YearMonth</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>本文の先頭キー（MandatoryLeaveMessages.key の戻り値。ワイルドカード不要）</t>
+          <t>確認する年月（JST の暦月）</t>
         </is>
       </c>
       <c r="D57" s="8" t="n"/>
@@ -6999,21 +7068,17 @@
       <c r="F57" s="9" t="n"/>
     </row>
     <row r="58" ht="19" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>yearMonth</t>
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>戻り値</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>YearMonth</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>確認する年月（JST の暦月）</t>
-        </is>
-      </c>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="n"/>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
       <c r="F58" s="9" t="n"/>
@@ -7021,12 +7086,12 @@
     <row r="59" ht="19" customHeight="1">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>戻り値</t>
+          <t>例外</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>DataAccessException</t>
         </is>
       </c>
       <c r="C59" s="8" t="n"/>
@@ -7037,12 +7102,12 @@
     <row r="60" ht="19" customHeight="1">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>例外</t>
+          <t>トランザクション</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>DataAccessException</t>
+          <t>@Transactional(readOnly = true)（Service）</t>
         </is>
       </c>
       <c r="C60" s="8" t="n"/>
@@ -7050,29 +7115,13 @@
       <c r="E60" s="8" t="n"/>
       <c r="F60" s="9" t="n"/>
     </row>
-    <row r="61" ht="19" customHeight="1">
+    <row r="61" ht="184" customHeight="1">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>トランザクション</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>@Transactional(readOnly = true)（Service）</t>
-        </is>
-      </c>
-      <c r="C61" s="8" t="n"/>
-      <c r="D61" s="8" t="n"/>
-      <c r="E61" s="8" t="n"/>
-      <c r="F61" s="9" t="n"/>
-    </row>
-    <row r="62" ht="184" customHeight="1">
-      <c r="A62" s="10" t="inlineStr">
-        <is>
           <t>処理詳細（疑似コード）</t>
         </is>
       </c>
-      <c r="B62" s="15" t="inlineStr">
+      <c r="B61" s="15" t="inlineStr">
         <is>
           <t>public boolean existsMonthly(Long userId, String type, String keyPrefix, YearMonth yearMonth) {
     LocalDateTime from = yearMonth.atDay(1).atStartOfDay();                    // 当月 1 日 00:00:00（JST）
@@ -7088,20 +7137,37 @@
  LIMIT 1</t>
         </is>
       </c>
+      <c r="C61" s="8" t="n"/>
+      <c r="D61" s="8" t="n"/>
+      <c r="E61" s="8" t="n"/>
+      <c r="F61" s="9" t="n"/>
+    </row>
+    <row r="62" ht="19" customHeight="1">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>呼出先</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="C62" s="8" t="n"/>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="9" t="n"/>
     </row>
-    <row r="63" ht="19" customHeight="1">
+    <row r="63" ht="34" customHeight="1">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>呼出先</t>
+          <t>呼出元</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MandatoryLeaveAlertUnitService#alertOne（BAT-002）
+NotificationService#existsMonthly（4引数 overload）/ existsBy…MessageStartingWith…（BAT-002）</t>
         </is>
       </c>
       <c r="C63" s="8" t="n"/>
@@ -7112,12 +7178,12 @@
     <row r="64" ht="19" customHeight="1">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>呼出元</t>
+          <t>関連 ONL</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>なし（外部 API／フレームワークから起動、またはテストのみ）</t>
+          <t>BAT-002 年5日取得義務アラート（バッチ）、ONL-019 通知一覧取得（API-019）</t>
         </is>
       </c>
       <c r="C64" s="8" t="n"/>
@@ -7125,15 +7191,18 @@
       <c r="E64" s="8" t="n"/>
       <c r="F64" s="9" t="n"/>
     </row>
-    <row r="65" ht="19" customHeight="1">
+    <row r="65" ht="124" customHeight="1">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>関連 ONL</t>
+          <t>備考</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>BAT-002 年5日取得義務アラート（バッチ）</t>
+          <t>【ONL-019 との関係】ONL-019 の existsMonthly(Long userId, String type, YearMonth yearMonth) は『宛先・type・月』だけで判定し、対象者・付与日を区別できない。管理者は同じ月に複数の対象者分を受け取るため、3 引数版を使うと 2 人目以降が『送信済み』と誤判定されて通知されない。そのため BAT-002 は keyPrefix を加えた本 overload を使う。ONL-019 への追記が必要（最終報告に記載）。3 引数版は本書では使用しない。
+同時に走った場合の厳密な排他は無い（D-6）。
+idx_notif_user (user_id, is_read) が user_id で効く。1 ユーザーの通知は多くて年数百件のため type・前方一致・月範囲の絞り込みで問題ない。
+created_at は DB の DEFAULT CURRENT_TIMESTAMP。DB セッションの JST は hikari connection-init-sql で設定済み（7.3）のため、JST の暦月で判定できる。</t>
         </is>
       </c>
       <c r="C65" s="8" t="n"/>
@@ -7141,18 +7210,27 @@
       <c r="E65" s="8" t="n"/>
       <c r="F65" s="9" t="n"/>
     </row>
-    <row r="66" ht="124" customHeight="1">
+    <row r="66" ht="259" customHeight="1">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>他 ONL の記述
+（ONL-019）</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>【ONL-019 との関係】ONL-019 の existsMonthly(Long userId, String type, YearMonth yearMonth) は『宛先・type・月』だけで判定し、対象者・付与日を区別できない。管理者は同じ月に複数の対象者分を受け取るため、3 引数版を使うと 2 人目以降が『送信済み』と誤判定されて通知されない。そのため BAT-002 は keyPrefix を加えた本 overload を使う。ONL-019 への追記が必要（最終報告に記載）。3 引数版は本書では使用しない。
-同時に走った場合の厳密な排他は無い（D-6）。
-idx_notif_user (user_id, is_read) が user_id で効く。1 ユーザーの通知は多くて年数百件のため type・前方一致・月範囲の絞り込みで問題ない。
-created_at は DB の DEFAULT CURRENT_TIMESTAMP。DB セッションの JST は hikari connection-init-sql で設定済み（7.3）のため、JST の暦月で判定できる。</t>
+          <t>例外: なし（引数 null は NullPointerException＝呼出し側のバグ → E-012）
+アノテーション: @Transactional(readOnly = true)  ※クラスに @Service
+処理詳細（差分あり）:
+LocalDateTime from = yearMonth.atDay(1).atStartOfDay();
+LocalDateTime to = yearMonth.plusMonths(1).atDay(1).atStartOfDay();
+return notificationRepository
+        .existsByUserIdAndTypeAndMessageStartingWithAndCreatedAtGreaterThanEqualAndCreatedAtLessThan(
+                userId, type, keyPrefix, from, to);
+備考: 【3 引数版との違い】3 引数版は『宛先・type・月』だけで判定し、対象者・付与日を区別できない。管理者は同じ月に複数の対象者分を受け取るため、3 引数版を使うと 2 人目以降が『送信済み』と誤判定される。BAT-002 は本 overload を使い、本文先頭のキーで対象者・付与日を区別する（キーは ']' で閉じるので ID:1 と ID:12 が混ざらない）。3 引数版は互換のため残す（keyPrefix を渡さない呼出し用）。
+【呼出し元の例（BAT-002）】if (!notificationService.existsMonthly(toUserId, NotificationType.LEAVE_ALERT, key, ym)) notificationService.notify(toUserId, NotificationType.LEAVE_ALERT, message, null);  key = "[対象者ID:12 付与日:2025-10-01]" を message の先頭に置く。
+同時実行時の厳密な排他は無い（DB 制約ではない）。
+idx_notif_user (user_id, is_read) が user_id で効く。1 ユーザーの通知は多くて年数百件のため type・前方一致・月範囲の絞り込みで問題ない。</t>
         </is>
       </c>
       <c r="C66" s="8" t="n"/>
@@ -7163,7 +7241,7 @@
     <row r="67" ht="19" customHeight="1">
       <c r="A67" s="14" t="inlineStr">
         <is>
-          <t>③-2-2  NotificationService#existsMonthly  （一覧 No. 2）</t>
+          <t>③-2-2  NotificationService#notify  （一覧 No. 2）</t>
         </is>
       </c>
       <c r="B67" s="8" t="n"/>
@@ -7180,7 +7258,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Service（BAT-002 の求めで ONL-019 が追加する overload。3 引数版も残す）</t>
+          <t>Service（新規・共有。全 ONL の通知登録の唯一の入口。疑似コードの定義元は本書）</t>
         </is>
       </c>
       <c r="C68" s="8" t="n"/>
@@ -7196,8 +7274,8 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>@Transactional(readOnly = true)
-public boolean existsMonthly(Long userId, String type, String keyPrefix, YearMonth yearMonth)</t>
+          <t>@Transactional(propagation = Propagation.REQUIRED)
+public void notify(Long userId, String type, String message, Long requestId)</t>
         </is>
       </c>
       <c r="C69" s="8" t="n"/>
@@ -7213,7 +7291,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>指定ユーザー・指定種別の通知のうち、本文が keyPrefix で始まるもの（対象者・付与日が同じもの）が、指定した年月（JST）に既に作成されているかを返す。</t>
+          <t>宛先ユーザーへ画面内通知を1件登録する。type（通知種別）と requestId（関連する申請ID。無ければ null）を notifications に保存し、画面は requestId があれば SCR-106 の該当申請へ遷移できる。</t>
         </is>
       </c>
       <c r="C70" s="8" t="n"/>
@@ -7229,7 +7307,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>@Transactional(readOnly = true)  ※クラスに @Service</t>
+          <t>クラス: @Service。メソッド: @Transactional(propagation = REQUIRED)  ※呼出し元のトランザクションに参加する（REQUIRES_NEW にしない）</t>
         </is>
       </c>
       <c r="C71" s="8" t="n"/>
@@ -7270,7 +7348,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>通知先ユーザーID</t>
+          <t>通知先ユーザーID（必須）</t>
         </is>
       </c>
       <c r="D73" s="8" t="n"/>
@@ -7290,7 +7368,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>通知種別（BAT-002 は LEAVE_ALERT）</t>
+          <t>通知種別。NotificationType の7値のいずれか（必須）</t>
         </is>
       </c>
       <c r="D74" s="8" t="n"/>
@@ -7300,7 +7378,7 @@
     <row r="75" ht="19" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>keyPrefix</t>
+          <t>message</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -7310,7 +7388,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>message の前方一致キー。BAT-002 は『[対象者ID:{id} 付与日:{yyyy-MM-dd}]』</t>
+          <t>通知本文（必須・空白のみ不可）。500文字を超える場合は切り詰める</t>
         </is>
       </c>
       <c r="D75" s="8" t="n"/>
@@ -7320,17 +7398,17 @@
     <row r="76" ht="19" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>yearMonth</t>
+          <t>requestId</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>YearMonth</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>確認する年月（JST の暦月）</t>
+          <t>関連する申請ID（REQUEST_* は必須、LEAVE_GRANTED / LEAVE_ALERT は null）</t>
         </is>
       </c>
       <c r="D76" s="8" t="n"/>
@@ -7345,7 +7423,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>boolean（1件以上あれば true）</t>
+          <t>なし（void）</t>
         </is>
       </c>
       <c r="C77" s="8" t="n"/>
@@ -7353,7 +7431,7 @@
       <c r="E77" s="8" t="n"/>
       <c r="F77" s="9" t="n"/>
     </row>
-    <row r="78" ht="19" customHeight="1">
+    <row r="78" ht="49" customHeight="1">
       <c r="A78" s="10" t="inlineStr">
         <is>
           <t>例外</t>
@@ -7361,7 +7439,8 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>なし（引数 null は NullPointerException＝呼出し側のバグ → E-012）</t>
+          <t>IllegalArgumentException（userId が null／type が不明・null／message が空／REQUEST_* で requestId が null。呼出し側のバグ → E-012 / 500）
+DataIntegrityViolationException（FK 違反。→ E-012）</t>
         </is>
       </c>
       <c r="C78" s="8" t="n"/>
@@ -7377,7 +7456,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>@Transactional(readOnly = true)  ※クラスに @Service</t>
+          <t>@Transactional(propagation = REQUIRED)  ※呼出し元のトランザクションに参加する（REQUIRES_NEW にしない）</t>
         </is>
       </c>
       <c r="C79" s="8" t="n"/>
@@ -7385,7 +7464,7 @@
       <c r="E79" s="8" t="n"/>
       <c r="F79" s="9" t="n"/>
     </row>
-    <row r="80" ht="184" customHeight="1">
+    <row r="80" ht="199" customHeight="1">
       <c r="A80" s="10" t="inlineStr">
         <is>
           <t>処理詳細（疑似コード）</t>
@@ -7393,18 +7472,19 @@
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>public boolean existsMonthly(Long userId, String type, String keyPrefix, YearMonth yearMonth) {
-    LocalDateTime from = yearMonth.atDay(1).atStartOfDay();                    // 当月 1 日 00:00:00（JST）
-    LocalDateTime to   = yearMonth.plusMonths(1).atDay(1).atStartOfDay();      // 翌月 1 日 00:00:00（含まない）
-    return notificationRepository
-        .existsByUserIdAndTypeAndMessageStartingWithAndCreatedAtGreaterThanEqualAndCreatedAtLessThan(
-            userId, type, keyPrefix, from, to);
-}
--- 実行される SQL（StartingWith は param || '%' に変換され、% _ \ はエスケープされる）
-SELECT 1 FROM notifications
- WHERE user_id = ? AND type = ? AND message LIKE ? ESCAPE '\'
-   AND created_at &gt;= ? AND created_at &lt; ?
- LIMIT 1</t>
+          <t>if (userId == null) throw new IllegalArgumentException("userId is required");
+if (type == null || !NotificationType.ALL.contains(type))
+    throw new IllegalArgumentException("unknown notification type: " + type);
+if (NotificationType.REQUEST_BOUND.contains(type) &amp;&amp; requestId == null)
+    throw new IllegalArgumentException("requestId is required for " + type);
+if (message == null || message.isBlank()) throw new IllegalArgumentException("message is required");
+Notification n = new Notification();
+n.setUserId(userId);
+n.setType(type);
+n.setRequestId(requestId);
+n.setMessage(message.length() &gt; MESSAGE_MAX ? message.substring(0, MESSAGE_MAX) : message);
+n.setRead(false);
+notificationRepository.save(n);</t>
         </is>
       </c>
       <c r="C80" s="8" t="n"/>
@@ -7420,7 +7500,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>NotificationRepository#existsByUserIdAndTypeAndMessageStartingWithAndCreatedAtGreaterThanEqualAndCreatedAtLessThan</t>
+          <t>NotificationRepository#save（JpaRepository）</t>
         </is>
       </c>
       <c r="C81" s="8" t="n"/>
@@ -7428,387 +7508,13 @@
       <c r="E81" s="8" t="n"/>
       <c r="F81" s="9" t="n"/>
     </row>
-    <row r="82" ht="34" customHeight="1">
+    <row r="82" ht="109" customHeight="1">
       <c r="A82" s="10" t="inlineStr">
         <is>
           <t>呼出元</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>MandatoryLeaveAlertUnitService#alertOne（BAT-002）
-NotificationService#existsMonthly（4引数 overload）/ existsBy…MessageStartingWith…（BAT-002）</t>
-        </is>
-      </c>
-      <c r="C82" s="8" t="n"/>
-      <c r="D82" s="8" t="n"/>
-      <c r="E82" s="8" t="n"/>
-      <c r="F82" s="9" t="n"/>
-    </row>
-    <row r="83" ht="19" customHeight="1">
-      <c r="A83" s="10" t="inlineStr">
-        <is>
-          <t>関連 ONL</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>BAT-002 年5日取得義務アラート（バッチ）、ONL-019 通知一覧取得（API-019）</t>
-        </is>
-      </c>
-      <c r="C83" s="8" t="n"/>
-      <c r="D83" s="8" t="n"/>
-      <c r="E83" s="8" t="n"/>
-      <c r="F83" s="9" t="n"/>
-    </row>
-    <row r="84" ht="139" customHeight="1">
-      <c r="A84" s="10" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>【3 引数版との違い】3 引数版は『宛先・type・月』だけで判定し、対象者・付与日を区別できない。管理者は同じ月に複数の対象者分を受け取るため、3 引数版を使うと 2 人目以降が『送信済み』と誤判定される。BAT-002 は本 overload を使い、本文先頭のキーで対象者・付与日を区別する（キーは ']' で閉じるので ID:1 と ID:12 が混ざらない）。3 引数版は互換のため残す（keyPrefix を渡さない呼出し用）。
-【呼出し元の例（BAT-002）】if (!notificationService.existsMonthly(toUserId, NotificationType.LEAVE_ALERT, key, ym)) notificationService.notify(toUserId, NotificationType.LEAVE_ALERT, message, null);  key = "[対象者ID:12 付与日:2025-10-01]" を message の先頭に置く。
-同時実行時の厳密な排他は無い（DB 制約ではない）。
-idx_notif_user (user_id, is_read) が user_id で効く。1 ユーザーの通知は多くて年数百件のため type・前方一致・月範囲の絞り込みで問題ない。</t>
-        </is>
-      </c>
-      <c r="C84" s="8" t="n"/>
-      <c r="D84" s="8" t="n"/>
-      <c r="E84" s="8" t="n"/>
-      <c r="F84" s="9" t="n"/>
-    </row>
-    <row r="85" ht="169" customHeight="1">
-      <c r="A85" s="10" t="inlineStr">
-        <is>
-          <t>他 ONL の記述
-（BAT-002）</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>例外: DataAccessException
-アノテーション: @Transactional(readOnly = true)（Service）
-備考: 【ONL-019 との関係】ONL-019 の existsMonthly(Long userId, String type, YearMonth yearMonth) は『宛先・type・月』だけで判定し、対象者・付与日を区別できない。管理者は同じ月に複数の対象者分を受け取るため、3 引数版を使うと 2 人目以降が『送信済み』と誤判定されて通知されない。そのため BAT-002 は keyPrefix を加えた本 overload を使う。ONL-019 への追記が必要（最終報告に記載）。3 引数版は本書では使用しない。
-同時に走った場合の厳密な排他は無い（D-6）。
-idx_notif_user (user_id, is_read) が user_id で効く。1 ユーザーの通知は多くて年数百件のため type・前方一致・月範囲の絞り込みで問題ない。
-created_at は DB の DEFAULT CURRENT_TIMESTAMP。DB セッションの JST は hikari connection-init-sql で設定済み（7.3）のため、JST の暦月で判定できる。</t>
-        </is>
-      </c>
-      <c r="C85" s="8" t="n"/>
-      <c r="D85" s="8" t="n"/>
-      <c r="E85" s="8" t="n"/>
-      <c r="F85" s="9" t="n"/>
-    </row>
-    <row r="86" ht="19" customHeight="1">
-      <c r="A86" s="14" t="inlineStr">
-        <is>
-          <t>③-2-3  NotificationService#notify  （一覧 No. 3）</t>
-        </is>
-      </c>
-      <c r="B86" s="8" t="n"/>
-      <c r="C86" s="8" t="n"/>
-      <c r="D86" s="8" t="n"/>
-      <c r="E86" s="8" t="n"/>
-      <c r="F86" s="9" t="n"/>
-    </row>
-    <row r="87" ht="19" customHeight="1">
-      <c r="A87" s="10" t="inlineStr">
-        <is>
-          <t>種別</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>Service（新規・共有。全 ONL の通知登録の唯一の入口。疑似コードの定義元は本書）</t>
-        </is>
-      </c>
-      <c r="C87" s="8" t="n"/>
-      <c r="D87" s="8" t="n"/>
-      <c r="E87" s="8" t="n"/>
-      <c r="F87" s="9" t="n"/>
-    </row>
-    <row r="88" ht="34" customHeight="1">
-      <c r="A88" s="10" t="inlineStr">
-        <is>
-          <t>シグネチャ</t>
-        </is>
-      </c>
-      <c r="B88" s="15" t="inlineStr">
-        <is>
-          <t>@Transactional(propagation = Propagation.REQUIRED)
-public void notify(Long userId, String type, String message, Long requestId)</t>
-        </is>
-      </c>
-      <c r="C88" s="8" t="n"/>
-      <c r="D88" s="8" t="n"/>
-      <c r="E88" s="8" t="n"/>
-      <c r="F88" s="9" t="n"/>
-    </row>
-    <row r="89" ht="34" customHeight="1">
-      <c r="A89" s="10" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>宛先ユーザーへ画面内通知を1件登録する。type（通知種別）と requestId（関連する申請ID。無ければ null）を notifications に保存し、画面は requestId があれば SCR-106 の該当申請へ遷移できる。</t>
-        </is>
-      </c>
-      <c r="C89" s="8" t="n"/>
-      <c r="D89" s="8" t="n"/>
-      <c r="E89" s="8" t="n"/>
-      <c r="F89" s="9" t="n"/>
-    </row>
-    <row r="90" ht="19" customHeight="1">
-      <c r="A90" s="10" t="inlineStr">
-        <is>
-          <t>アノテーション</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>クラス: @Service。メソッド: @Transactional(propagation = REQUIRED)  ※呼出し元のトランザクションに参加する（REQUIRES_NEW にしない）</t>
-        </is>
-      </c>
-      <c r="C90" s="8" t="n"/>
-      <c r="D90" s="8" t="n"/>
-      <c r="E90" s="8" t="n"/>
-      <c r="F90" s="9" t="n"/>
-    </row>
-    <row r="91" ht="19" customHeight="1">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>引数名</t>
-        </is>
-      </c>
-      <c r="B91" s="6" t="inlineStr">
-        <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="D91" s="8" t="n"/>
-      <c r="E91" s="8" t="n"/>
-      <c r="F91" s="9" t="n"/>
-    </row>
-    <row r="92" ht="19" customHeight="1">
-      <c r="A92" s="4" t="inlineStr">
-        <is>
-          <t>userId</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>通知先ユーザーID（必須）</t>
-        </is>
-      </c>
-      <c r="D92" s="8" t="n"/>
-      <c r="E92" s="8" t="n"/>
-      <c r="F92" s="9" t="n"/>
-    </row>
-    <row r="93" ht="19" customHeight="1">
-      <c r="A93" s="4" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>通知種別。NotificationType の7値のいずれか（必須）</t>
-        </is>
-      </c>
-      <c r="D93" s="8" t="n"/>
-      <c r="E93" s="8" t="n"/>
-      <c r="F93" s="9" t="n"/>
-    </row>
-    <row r="94" ht="19" customHeight="1">
-      <c r="A94" s="4" t="inlineStr">
-        <is>
-          <t>message</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="C94" s="4" t="inlineStr">
-        <is>
-          <t>通知本文（必須・空白のみ不可）。500文字を超える場合は切り詰める</t>
-        </is>
-      </c>
-      <c r="D94" s="8" t="n"/>
-      <c r="E94" s="8" t="n"/>
-      <c r="F94" s="9" t="n"/>
-    </row>
-    <row r="95" ht="19" customHeight="1">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>requestId</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>関連する申請ID（REQUEST_* は必須、LEAVE_GRANTED / LEAVE_ALERT は null）</t>
-        </is>
-      </c>
-      <c r="D95" s="8" t="n"/>
-      <c r="E95" s="8" t="n"/>
-      <c r="F95" s="9" t="n"/>
-    </row>
-    <row r="96" ht="19" customHeight="1">
-      <c r="A96" s="10" t="inlineStr">
-        <is>
-          <t>戻り値</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>なし（void）</t>
-        </is>
-      </c>
-      <c r="C96" s="8" t="n"/>
-      <c r="D96" s="8" t="n"/>
-      <c r="E96" s="8" t="n"/>
-      <c r="F96" s="9" t="n"/>
-    </row>
-    <row r="97" ht="49" customHeight="1">
-      <c r="A97" s="10" t="inlineStr">
-        <is>
-          <t>例外</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>IllegalArgumentException（userId が null／type が不明・null／message が空／REQUEST_* で requestId が null。呼出し側のバグ → E-012 / 500）
-DataIntegrityViolationException（FK 違反。→ E-012）</t>
-        </is>
-      </c>
-      <c r="C97" s="8" t="n"/>
-      <c r="D97" s="8" t="n"/>
-      <c r="E97" s="8" t="n"/>
-      <c r="F97" s="9" t="n"/>
-    </row>
-    <row r="98" ht="19" customHeight="1">
-      <c r="A98" s="10" t="inlineStr">
-        <is>
-          <t>トランザクション</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>@Transactional(propagation = REQUIRED)  ※呼出し元のトランザクションに参加する（REQUIRES_NEW にしない）</t>
-        </is>
-      </c>
-      <c r="C98" s="8" t="n"/>
-      <c r="D98" s="8" t="n"/>
-      <c r="E98" s="8" t="n"/>
-      <c r="F98" s="9" t="n"/>
-    </row>
-    <row r="99" ht="364" customHeight="1">
-      <c r="A99" s="10" t="inlineStr">
-        <is>
-          <t>処理詳細（疑似コード）</t>
-        </is>
-      </c>
-      <c r="B99" s="15" t="inlineStr">
-        <is>
-          <t>@Service
-public class NotificationService {
-    static final int MESSAGE_MAX = 500;
-    private final NotificationRepository notificationRepository;     // コンストラクタインジェクション
-    @Transactional(propagation = Propagation.REQUIRED)
-    public void notify(Long userId, String type, String message, Long requestId) {
-        if (userId == null)
-            throw new IllegalArgumentException("userId is required");
-        if (type == null || !NotificationType.ALL.contains(type))
-            throw new IllegalArgumentException("unknown notification type: " + type);
-        if (NotificationType.REQUEST_BOUND.contains(type) &amp;&amp; requestId == null)
-            throw new IllegalArgumentException("requestId is required for " + type);
-        if (message == null || message.isBlank())
-            throw new IllegalArgumentException("message is required");
-        Notification n = new Notification();
-        n.setUserId(userId);
-        n.setType(type);
-        n.setRequestId(requestId);                       // 申請に紐づかない通知（LEAVE_*）は null
-        n.setMessage(truncate(message.strip(), MESSAGE_MAX));   // VARCHAR(500)
-        n.setRead(false);                                // is_read = FALSE
-        notificationRepository.save(n);                  // INSERT INTO notifications (user_id, type, request_id, message, is_read)
-    }</t>
-        </is>
-      </c>
-      <c r="C99" s="8" t="n"/>
-      <c r="D99" s="8" t="n"/>
-      <c r="E99" s="8" t="n"/>
-      <c r="F99" s="9" t="n"/>
-    </row>
-    <row r="100" ht="94" customHeight="1">
-      <c r="A100" s="10" t="inlineStr">
-        <is>
-          <t>（続き）</t>
-        </is>
-      </c>
-      <c r="B100" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-    static String truncate(String s, int max) {         // コードポイント単位で切り詰める
-        if (s.codePointCount(0, s.length()) &lt;= max) return s;
-        return s.substring(0, s.offsetByCodePoints(0, max - 1)) + "…";
-    }
-}</t>
-        </is>
-      </c>
-      <c r="C100" s="8" t="n"/>
-      <c r="D100" s="8" t="n"/>
-      <c r="E100" s="8" t="n"/>
-      <c r="F100" s="9" t="n"/>
-    </row>
-    <row r="101" ht="19" customHeight="1">
-      <c r="A101" s="10" t="inlineStr">
-        <is>
-          <t>呼出先</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>NotificationRepository#save（JpaRepository）</t>
-        </is>
-      </c>
-      <c r="C101" s="8" t="n"/>
-      <c r="D101" s="8" t="n"/>
-      <c r="E101" s="8" t="n"/>
-      <c r="F101" s="9" t="n"/>
-    </row>
-    <row r="102" ht="109" customHeight="1">
-      <c r="A102" s="10" t="inlineStr">
-        <is>
-          <t>呼出元</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="inlineStr">
         <is>
           <t>ApprovalService#notifyApplicant / notifyApprovers / describe（ONL-010）
 LeaveBalanceService#adjust（ONL-017）
@@ -7819,34 +7525,34 @@
 RequestService#withdraw（ONL-008）</t>
         </is>
       </c>
-      <c r="C102" s="8" t="n"/>
-      <c r="D102" s="8" t="n"/>
-      <c r="E102" s="8" t="n"/>
-      <c r="F102" s="9" t="n"/>
-    </row>
-    <row r="103" ht="19" customHeight="1">
-      <c r="A103" s="10" t="inlineStr">
+      <c r="C82" s="8" t="n"/>
+      <c r="D82" s="8" t="n"/>
+      <c r="E82" s="8" t="n"/>
+      <c r="F82" s="9" t="n"/>
+    </row>
+    <row r="83" ht="19" customHeight="1">
+      <c r="A83" s="10" t="inlineStr">
         <is>
           <t>関連 ONL</t>
         </is>
       </c>
-      <c r="B103" s="4" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>ONL-005 申請作成（API-005）</t>
         </is>
       </c>
-      <c r="C103" s="8" t="n"/>
-      <c r="D103" s="8" t="n"/>
-      <c r="E103" s="8" t="n"/>
-      <c r="F103" s="9" t="n"/>
-    </row>
-    <row r="104" ht="109" customHeight="1">
-      <c r="A104" s="10" t="inlineStr">
+      <c r="C83" s="8" t="n"/>
+      <c r="D83" s="8" t="n"/>
+      <c r="E83" s="8" t="n"/>
+      <c r="F83" s="9" t="n"/>
+    </row>
+    <row r="84" ht="109" customHeight="1">
+      <c r="A84" s="10" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="B104" s="4" t="inlineStr">
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t>【呼出し元の一覧】ONL-005 / ONL-022 → REQUEST_SUBMITTED（現在の承認者）、ONL-010 → REQUEST_APPROVED（申請者。1段目承認時も同種別で本文を変える）・REQUEST_SUBMITTED（2段目の承認者）、ONL-011 → REQUEST_RETURNED、ONL-012 → REQUEST_REJECTED、ONL-008 → REQUEST_WITHDRAWN（取下げ時の現在の承認者）、ONL-017 → LEAVE_GRANTED、BAT-001 → LEAVE_GRANTED、BAT-002 → LEAVE_ALERT。
 requests の行を INSERT した後（同一トランザクション内）に呼ぶこと。requestId の FK（fk_notifications_request_id）は requests に行があることが前提。
@@ -7854,182 +7560,182 @@
 本メソッドは通知の重複判定を行わない。月次の重複防止が必要な呼出し元（BAT-002）は ONL-019 の existsMonthly で事前確認する。</t>
         </is>
       </c>
-      <c r="C104" s="8" t="n"/>
-      <c r="D104" s="8" t="n"/>
-      <c r="E104" s="8" t="n"/>
-      <c r="F104" s="9" t="n"/>
-    </row>
-    <row r="105" ht="19" customHeight="1">
-      <c r="A105" s="14" t="inlineStr">
-        <is>
-          <t>③-2-4  NotificationService#getNotifications  （一覧 No. 4）</t>
-        </is>
-      </c>
-      <c r="B105" s="8" t="n"/>
-      <c r="C105" s="8" t="n"/>
-      <c r="D105" s="8" t="n"/>
-      <c r="E105" s="8" t="n"/>
-      <c r="F105" s="9" t="n"/>
-    </row>
-    <row r="106" ht="19" customHeight="1">
-      <c r="A106" s="10" t="inlineStr">
+      <c r="C84" s="8" t="n"/>
+      <c r="D84" s="8" t="n"/>
+      <c r="E84" s="8" t="n"/>
+      <c r="F84" s="9" t="n"/>
+    </row>
+    <row r="85" ht="19" customHeight="1">
+      <c r="A85" s="14" t="inlineStr">
+        <is>
+          <t>③-2-3  NotificationService#getNotifications  （一覧 No. 3）</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="n"/>
+      <c r="C85" s="8" t="n"/>
+      <c r="D85" s="8" t="n"/>
+      <c r="E85" s="8" t="n"/>
+      <c r="F85" s="9" t="n"/>
+    </row>
+    <row r="86" ht="19" customHeight="1">
+      <c r="A86" s="10" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="B106" s="4" t="inlineStr">
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t>Service（ONL-019 一覧）</t>
         </is>
       </c>
-      <c r="C106" s="8" t="n"/>
-      <c r="D106" s="8" t="n"/>
-      <c r="E106" s="8" t="n"/>
-      <c r="F106" s="9" t="n"/>
-    </row>
-    <row r="107" ht="19" customHeight="1">
-      <c r="A107" s="10" t="inlineStr">
+      <c r="C86" s="8" t="n"/>
+      <c r="D86" s="8" t="n"/>
+      <c r="E86" s="8" t="n"/>
+      <c r="F86" s="9" t="n"/>
+    </row>
+    <row r="87" ht="19" customHeight="1">
+      <c r="A87" s="10" t="inlineStr">
         <is>
           <t>シグネチャ</t>
         </is>
       </c>
-      <c r="B107" s="15" t="inlineStr">
+      <c r="B87" s="15" t="inlineStr">
         <is>
           <t>public NotificationListResponse getNotifications(Long userId)</t>
         </is>
       </c>
-      <c r="C107" s="8" t="n"/>
-      <c r="D107" s="8" t="n"/>
-      <c r="E107" s="8" t="n"/>
-      <c r="F107" s="9" t="n"/>
-    </row>
-    <row r="108" ht="19" customHeight="1">
-      <c r="A108" s="10" t="inlineStr">
+      <c r="C87" s="8" t="n"/>
+      <c r="D87" s="8" t="n"/>
+      <c r="E87" s="8" t="n"/>
+      <c r="F87" s="9" t="n"/>
+    </row>
+    <row r="88" ht="19" customHeight="1">
+      <c r="A88" s="10" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
       </c>
-      <c r="B108" s="4" t="inlineStr">
+      <c r="B88" s="4" t="inlineStr">
         <is>
           <t>本人宛の通知を新しい順に最大50件取得し、応答 DTO に変換して返す。</t>
         </is>
       </c>
-      <c r="C108" s="8" t="n"/>
-      <c r="D108" s="8" t="n"/>
-      <c r="E108" s="8" t="n"/>
-      <c r="F108" s="9" t="n"/>
-    </row>
-    <row r="109" ht="19" customHeight="1">
-      <c r="A109" s="10" t="inlineStr">
+      <c r="C88" s="8" t="n"/>
+      <c r="D88" s="8" t="n"/>
+      <c r="E88" s="8" t="n"/>
+      <c r="F88" s="9" t="n"/>
+    </row>
+    <row r="89" ht="19" customHeight="1">
+      <c r="A89" s="10" t="inlineStr">
         <is>
           <t>アノテーション</t>
         </is>
       </c>
-      <c r="B109" s="4" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>@Transactional(readOnly = true)  ※クラスに @Service</t>
         </is>
       </c>
-      <c r="C109" s="8" t="n"/>
-      <c r="D109" s="8" t="n"/>
-      <c r="E109" s="8" t="n"/>
-      <c r="F109" s="9" t="n"/>
-    </row>
-    <row r="110" ht="19" customHeight="1">
-      <c r="A110" s="6" t="inlineStr">
+      <c r="C89" s="8" t="n"/>
+      <c r="D89" s="8" t="n"/>
+      <c r="E89" s="8" t="n"/>
+      <c r="F89" s="9" t="n"/>
+    </row>
+    <row r="90" ht="19" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>引数名</t>
         </is>
       </c>
-      <c r="B110" s="6" t="inlineStr">
+      <c r="B90" s="6" t="inlineStr">
         <is>
           <t>型</t>
         </is>
       </c>
-      <c r="C110" s="6" t="inlineStr">
+      <c r="C90" s="6" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
       </c>
-      <c r="D110" s="8" t="n"/>
-      <c r="E110" s="8" t="n"/>
-      <c r="F110" s="9" t="n"/>
-    </row>
-    <row r="111" ht="19" customHeight="1">
-      <c r="A111" s="4" t="inlineStr">
+      <c r="D90" s="8" t="n"/>
+      <c r="E90" s="8" t="n"/>
+      <c r="F90" s="9" t="n"/>
+    </row>
+    <row r="91" ht="19" customHeight="1">
+      <c r="A91" s="4" t="inlineStr">
         <is>
           <t>userId</t>
         </is>
       </c>
-      <c r="B111" s="4" t="inlineStr">
+      <c r="B91" s="4" t="inlineStr">
         <is>
           <t>Long</t>
         </is>
       </c>
-      <c r="C111" s="4" t="inlineStr">
+      <c r="C91" s="4" t="inlineStr">
         <is>
           <t>ログインユーザーID（JWT sub）。検索条件に必ず使う</t>
         </is>
       </c>
-      <c r="D111" s="8" t="n"/>
-      <c r="E111" s="8" t="n"/>
-      <c r="F111" s="9" t="n"/>
-    </row>
-    <row r="112" ht="19" customHeight="1">
-      <c r="A112" s="10" t="inlineStr">
+      <c r="D91" s="8" t="n"/>
+      <c r="E91" s="8" t="n"/>
+      <c r="F91" s="9" t="n"/>
+    </row>
+    <row r="92" ht="19" customHeight="1">
+      <c r="A92" s="10" t="inlineStr">
         <is>
           <t>戻り値</t>
         </is>
       </c>
-      <c r="B112" s="4" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>NotificationListResponse(notifications)。0件は空リスト</t>
         </is>
       </c>
-      <c r="C112" s="8" t="n"/>
-      <c r="D112" s="8" t="n"/>
-      <c r="E112" s="8" t="n"/>
-      <c r="F112" s="9" t="n"/>
-    </row>
-    <row r="113" ht="19" customHeight="1">
-      <c r="A113" s="10" t="inlineStr">
+      <c r="C92" s="8" t="n"/>
+      <c r="D92" s="8" t="n"/>
+      <c r="E92" s="8" t="n"/>
+      <c r="F92" s="9" t="n"/>
+    </row>
+    <row r="93" ht="19" customHeight="1">
+      <c r="A93" s="10" t="inlineStr">
         <is>
           <t>例外</t>
         </is>
       </c>
-      <c r="B113" s="4" t="inlineStr">
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
       </c>
-      <c r="C113" s="8" t="n"/>
-      <c r="D113" s="8" t="n"/>
-      <c r="E113" s="8" t="n"/>
-      <c r="F113" s="9" t="n"/>
-    </row>
-    <row r="114" ht="19" customHeight="1">
-      <c r="A114" s="10" t="inlineStr">
+      <c r="C93" s="8" t="n"/>
+      <c r="D93" s="8" t="n"/>
+      <c r="E93" s="8" t="n"/>
+      <c r="F93" s="9" t="n"/>
+    </row>
+    <row r="94" ht="19" customHeight="1">
+      <c r="A94" s="10" t="inlineStr">
         <is>
           <t>トランザクション</t>
         </is>
       </c>
-      <c r="B114" s="4" t="inlineStr">
+      <c r="B94" s="4" t="inlineStr">
         <is>
           <t>@Transactional(readOnly = true)  ※クラスに @Service</t>
         </is>
       </c>
-      <c r="C114" s="8" t="n"/>
-      <c r="D114" s="8" t="n"/>
-      <c r="E114" s="8" t="n"/>
-      <c r="F114" s="9" t="n"/>
-    </row>
-    <row r="115" ht="79" customHeight="1">
-      <c r="A115" s="10" t="inlineStr">
+      <c r="C94" s="8" t="n"/>
+      <c r="D94" s="8" t="n"/>
+      <c r="E94" s="8" t="n"/>
+      <c r="F94" s="9" t="n"/>
+    </row>
+    <row r="95" ht="79" customHeight="1">
+      <c r="A95" s="10" t="inlineStr">
         <is>
           <t>処理詳細（疑似コード）</t>
         </is>
       </c>
-      <c r="B115" s="15" t="inlineStr">
+      <c r="B95" s="15" t="inlineStr">
         <is>
           <t>List&lt;Notification&gt; rows = notificationRepository
     .findTop50ByUserIdOrderByCreatedAtDescIdDesc(userId);       // ③
@@ -8038,267 +7744,267 @@
 return new NotificationListResponse(list);                      // ⑤</t>
         </is>
       </c>
-      <c r="C115" s="8" t="n"/>
-      <c r="D115" s="8" t="n"/>
-      <c r="E115" s="8" t="n"/>
-      <c r="F115" s="9" t="n"/>
-    </row>
-    <row r="116" ht="19" customHeight="1">
-      <c r="A116" s="10" t="inlineStr">
+      <c r="C95" s="8" t="n"/>
+      <c r="D95" s="8" t="n"/>
+      <c r="E95" s="8" t="n"/>
+      <c r="F95" s="9" t="n"/>
+    </row>
+    <row r="96" ht="19" customHeight="1">
+      <c r="A96" s="10" t="inlineStr">
         <is>
           <t>呼出先</t>
         </is>
       </c>
-      <c r="B116" s="4" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>NotificationRepository#findTop50ByUserIdOrderByCreatedAtDescIdDesc / NotificationResponse#from</t>
         </is>
       </c>
-      <c r="C116" s="8" t="n"/>
-      <c r="D116" s="8" t="n"/>
-      <c r="E116" s="8" t="n"/>
-      <c r="F116" s="9" t="n"/>
-    </row>
-    <row r="117" ht="19" customHeight="1">
-      <c r="A117" s="10" t="inlineStr">
+      <c r="C96" s="8" t="n"/>
+      <c r="D96" s="8" t="n"/>
+      <c r="E96" s="8" t="n"/>
+      <c r="F96" s="9" t="n"/>
+    </row>
+    <row r="97" ht="19" customHeight="1">
+      <c r="A97" s="10" t="inlineStr">
         <is>
           <t>呼出元</t>
         </is>
       </c>
-      <c r="B117" s="4" t="inlineStr">
+      <c r="B97" s="4" t="inlineStr">
         <is>
           <t>NotificationController#list（ONL-019）</t>
         </is>
       </c>
-      <c r="C117" s="8" t="n"/>
-      <c r="D117" s="8" t="n"/>
-      <c r="E117" s="8" t="n"/>
-      <c r="F117" s="9" t="n"/>
-    </row>
-    <row r="118" ht="19" customHeight="1">
-      <c r="A118" s="10" t="inlineStr">
+      <c r="C97" s="8" t="n"/>
+      <c r="D97" s="8" t="n"/>
+      <c r="E97" s="8" t="n"/>
+      <c r="F97" s="9" t="n"/>
+    </row>
+    <row r="98" ht="19" customHeight="1">
+      <c r="A98" s="10" t="inlineStr">
         <is>
           <t>関連 ONL</t>
         </is>
       </c>
-      <c r="B118" s="4" t="inlineStr">
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t>ONL-019 通知一覧取得（API-019）</t>
         </is>
       </c>
-      <c r="C118" s="8" t="n"/>
-      <c r="D118" s="8" t="n"/>
-      <c r="E118" s="8" t="n"/>
-      <c r="F118" s="9" t="n"/>
-    </row>
-    <row r="119" ht="34" customHeight="1">
-      <c r="A119" s="10" t="inlineStr">
+      <c r="C98" s="8" t="n"/>
+      <c r="D98" s="8" t="n"/>
+      <c r="E98" s="8" t="n"/>
+      <c r="F98" s="9" t="n"/>
+    </row>
+    <row r="99" ht="34" customHeight="1">
+      <c r="A99" s="10" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="B119" s="4" t="inlineStr">
+      <c r="B99" s="4" t="inlineStr">
         <is>
           <t>一覧取得では既読化しない（既読化は POST のみ）。
 画面 SCR-101 は先頭5件だけを表示する（画面側で slice(0, 5)）。API は最大50件を返す（KF-DD-001）。ページングはなし。</t>
         </is>
       </c>
-      <c r="C119" s="8" t="n"/>
-      <c r="D119" s="8" t="n"/>
-      <c r="E119" s="8" t="n"/>
-      <c r="F119" s="9" t="n"/>
-    </row>
-    <row r="120" ht="19" customHeight="1">
-      <c r="A120" s="14" t="inlineStr">
-        <is>
-          <t>③-2-5  NotificationService#markAsRead  （一覧 No. 5）</t>
-        </is>
-      </c>
-      <c r="B120" s="8" t="n"/>
-      <c r="C120" s="8" t="n"/>
-      <c r="D120" s="8" t="n"/>
-      <c r="E120" s="8" t="n"/>
-      <c r="F120" s="9" t="n"/>
-    </row>
-    <row r="121" ht="19" customHeight="1">
-      <c r="A121" s="10" t="inlineStr">
+      <c r="C99" s="8" t="n"/>
+      <c r="D99" s="8" t="n"/>
+      <c r="E99" s="8" t="n"/>
+      <c r="F99" s="9" t="n"/>
+    </row>
+    <row r="100" ht="19" customHeight="1">
+      <c r="A100" s="14" t="inlineStr">
+        <is>
+          <t>③-2-4  NotificationService#markAsRead  （一覧 No. 4）</t>
+        </is>
+      </c>
+      <c r="B100" s="8" t="n"/>
+      <c r="C100" s="8" t="n"/>
+      <c r="D100" s="8" t="n"/>
+      <c r="E100" s="8" t="n"/>
+      <c r="F100" s="9" t="n"/>
+    </row>
+    <row r="101" ht="19" customHeight="1">
+      <c r="A101" s="10" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="B121" s="4" t="inlineStr">
+      <c r="B101" s="4" t="inlineStr">
         <is>
           <t>Service（ONL-019 既読化）</t>
         </is>
       </c>
-      <c r="C121" s="8" t="n"/>
-      <c r="D121" s="8" t="n"/>
-      <c r="E121" s="8" t="n"/>
-      <c r="F121" s="9" t="n"/>
-    </row>
-    <row r="122" ht="19" customHeight="1">
-      <c r="A122" s="10" t="inlineStr">
+      <c r="C101" s="8" t="n"/>
+      <c r="D101" s="8" t="n"/>
+      <c r="E101" s="8" t="n"/>
+      <c r="F101" s="9" t="n"/>
+    </row>
+    <row r="102" ht="19" customHeight="1">
+      <c r="A102" s="10" t="inlineStr">
         <is>
           <t>シグネチャ</t>
         </is>
       </c>
-      <c r="B122" s="15" t="inlineStr">
+      <c r="B102" s="15" t="inlineStr">
         <is>
           <t>public NotificationResponse markAsRead(Long userId, Long notificationId)</t>
         </is>
       </c>
-      <c r="C122" s="8" t="n"/>
-      <c r="D122" s="8" t="n"/>
-      <c r="E122" s="8" t="n"/>
-      <c r="F122" s="9" t="n"/>
-    </row>
-    <row r="123" ht="19" customHeight="1">
-      <c r="A123" s="10" t="inlineStr">
+      <c r="C102" s="8" t="n"/>
+      <c r="D102" s="8" t="n"/>
+      <c r="E102" s="8" t="n"/>
+      <c r="F102" s="9" t="n"/>
+    </row>
+    <row r="103" ht="19" customHeight="1">
+      <c r="A103" s="10" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
       </c>
-      <c r="B123" s="4" t="inlineStr">
+      <c r="B103" s="4" t="inlineStr">
         <is>
           <t>本人宛の通知であることを確認し、未読なら既読にして、通知1件を返す。</t>
         </is>
       </c>
-      <c r="C123" s="8" t="n"/>
-      <c r="D123" s="8" t="n"/>
-      <c r="E123" s="8" t="n"/>
-      <c r="F123" s="9" t="n"/>
-    </row>
-    <row r="124" ht="19" customHeight="1">
-      <c r="A124" s="10" t="inlineStr">
+      <c r="C103" s="8" t="n"/>
+      <c r="D103" s="8" t="n"/>
+      <c r="E103" s="8" t="n"/>
+      <c r="F103" s="9" t="n"/>
+    </row>
+    <row r="104" ht="19" customHeight="1">
+      <c r="A104" s="10" t="inlineStr">
         <is>
           <t>アノテーション</t>
         </is>
       </c>
-      <c r="B124" s="4" t="inlineStr">
+      <c r="B104" s="4" t="inlineStr">
         <is>
           <t>@Transactional  ※クラスに @Service。DB 更新を伴うため readOnly にしない</t>
         </is>
       </c>
-      <c r="C124" s="8" t="n"/>
-      <c r="D124" s="8" t="n"/>
-      <c r="E124" s="8" t="n"/>
-      <c r="F124" s="9" t="n"/>
-    </row>
-    <row r="125" ht="19" customHeight="1">
-      <c r="A125" s="6" t="inlineStr">
+      <c r="C104" s="8" t="n"/>
+      <c r="D104" s="8" t="n"/>
+      <c r="E104" s="8" t="n"/>
+      <c r="F104" s="9" t="n"/>
+    </row>
+    <row r="105" ht="19" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
         <is>
           <t>引数名</t>
         </is>
       </c>
-      <c r="B125" s="6" t="inlineStr">
+      <c r="B105" s="6" t="inlineStr">
         <is>
           <t>型</t>
         </is>
       </c>
-      <c r="C125" s="6" t="inlineStr">
+      <c r="C105" s="6" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
       </c>
-      <c r="D125" s="8" t="n"/>
-      <c r="E125" s="8" t="n"/>
-      <c r="F125" s="9" t="n"/>
-    </row>
-    <row r="126" ht="19" customHeight="1">
-      <c r="A126" s="4" t="inlineStr">
+      <c r="D105" s="8" t="n"/>
+      <c r="E105" s="8" t="n"/>
+      <c r="F105" s="9" t="n"/>
+    </row>
+    <row r="106" ht="19" customHeight="1">
+      <c r="A106" s="4" t="inlineStr">
         <is>
           <t>userId</t>
         </is>
       </c>
-      <c r="B126" s="4" t="inlineStr">
+      <c r="B106" s="4" t="inlineStr">
         <is>
           <t>Long</t>
         </is>
       </c>
-      <c r="C126" s="4" t="inlineStr">
+      <c r="C106" s="4" t="inlineStr">
         <is>
           <t>ログインユーザーID（JWT sub）</t>
         </is>
       </c>
-      <c r="D126" s="8" t="n"/>
-      <c r="E126" s="8" t="n"/>
-      <c r="F126" s="9" t="n"/>
-    </row>
-    <row r="127" ht="19" customHeight="1">
-      <c r="A127" s="4" t="inlineStr">
+      <c r="D106" s="8" t="n"/>
+      <c r="E106" s="8" t="n"/>
+      <c r="F106" s="9" t="n"/>
+    </row>
+    <row r="107" ht="19" customHeight="1">
+      <c r="A107" s="4" t="inlineStr">
         <is>
           <t>notificationId</t>
         </is>
       </c>
-      <c r="B127" s="4" t="inlineStr">
+      <c r="B107" s="4" t="inlineStr">
         <is>
           <t>Long</t>
         </is>
       </c>
-      <c r="C127" s="4" t="inlineStr">
+      <c r="C107" s="4" t="inlineStr">
         <is>
           <t>既読にする通知のID（パス）</t>
         </is>
       </c>
-      <c r="D127" s="8" t="n"/>
-      <c r="E127" s="8" t="n"/>
-      <c r="F127" s="9" t="n"/>
-    </row>
-    <row r="128" ht="19" customHeight="1">
-      <c r="A128" s="10" t="inlineStr">
+      <c r="D107" s="8" t="n"/>
+      <c r="E107" s="8" t="n"/>
+      <c r="F107" s="9" t="n"/>
+    </row>
+    <row r="108" ht="19" customHeight="1">
+      <c r="A108" s="10" t="inlineStr">
         <is>
           <t>戻り値</t>
         </is>
       </c>
-      <c r="B128" s="4" t="inlineStr">
+      <c r="B108" s="4" t="inlineStr">
         <is>
           <t>NotificationResponse（isRead = true）</t>
         </is>
       </c>
-      <c r="C128" s="8" t="n"/>
-      <c r="D128" s="8" t="n"/>
-      <c r="E128" s="8" t="n"/>
-      <c r="F128" s="9" t="n"/>
-    </row>
-    <row r="129" ht="19" customHeight="1">
-      <c r="A129" s="10" t="inlineStr">
+      <c r="C108" s="8" t="n"/>
+      <c r="D108" s="8" t="n"/>
+      <c r="E108" s="8" t="n"/>
+      <c r="F108" s="9" t="n"/>
+    </row>
+    <row r="109" ht="19" customHeight="1">
+      <c r="A109" s="10" t="inlineStr">
         <is>
           <t>例外</t>
         </is>
       </c>
-      <c r="B129" s="4" t="inlineStr">
+      <c r="B109" s="4" t="inlineStr">
         <is>
           <t>BusinessException("E-010", "この操作を行う権限がありません。", HttpStatus.FORBIDDEN)  ※通知が存在しない／他人の通知</t>
         </is>
       </c>
-      <c r="C129" s="8" t="n"/>
-      <c r="D129" s="8" t="n"/>
-      <c r="E129" s="8" t="n"/>
-      <c r="F129" s="9" t="n"/>
-    </row>
-    <row r="130" ht="19" customHeight="1">
-      <c r="A130" s="10" t="inlineStr">
+      <c r="C109" s="8" t="n"/>
+      <c r="D109" s="8" t="n"/>
+      <c r="E109" s="8" t="n"/>
+      <c r="F109" s="9" t="n"/>
+    </row>
+    <row r="110" ht="19" customHeight="1">
+      <c r="A110" s="10" t="inlineStr">
         <is>
           <t>トランザクション</t>
         </is>
       </c>
-      <c r="B130" s="4" t="inlineStr">
+      <c r="B110" s="4" t="inlineStr">
         <is>
           <t>@Transactional  ※クラスに @Service。DB 更新を伴うため readOnly にしない</t>
         </is>
       </c>
-      <c r="C130" s="8" t="n"/>
-      <c r="D130" s="8" t="n"/>
-      <c r="E130" s="8" t="n"/>
-      <c r="F130" s="9" t="n"/>
-    </row>
-    <row r="131" ht="154" customHeight="1">
-      <c r="A131" s="10" t="inlineStr">
+      <c r="C110" s="8" t="n"/>
+      <c r="D110" s="8" t="n"/>
+      <c r="E110" s="8" t="n"/>
+      <c r="F110" s="9" t="n"/>
+    </row>
+    <row r="111" ht="154" customHeight="1">
+      <c r="A111" s="10" t="inlineStr">
         <is>
           <t>処理詳細（疑似コード）</t>
         </is>
       </c>
-      <c r="B131" s="15" t="inlineStr">
+      <c r="B111" s="15" t="inlineStr">
         <is>
           <t>Notification n = notificationRepository
     .findByIdAndUserId(notificationId, userId)                   // ③ 本人の通知のみ
@@ -8312,66 +8018,66 @@
 return NotificationResponse.from(n);                            // ⑥</t>
         </is>
       </c>
-      <c r="C131" s="8" t="n"/>
-      <c r="D131" s="8" t="n"/>
-      <c r="E131" s="8" t="n"/>
-      <c r="F131" s="9" t="n"/>
-    </row>
-    <row r="132" ht="19" customHeight="1">
-      <c r="A132" s="10" t="inlineStr">
+      <c r="C111" s="8" t="n"/>
+      <c r="D111" s="8" t="n"/>
+      <c r="E111" s="8" t="n"/>
+      <c r="F111" s="9" t="n"/>
+    </row>
+    <row r="112" ht="19" customHeight="1">
+      <c r="A112" s="10" t="inlineStr">
         <is>
           <t>呼出先</t>
         </is>
       </c>
-      <c r="B132" s="4" t="inlineStr">
+      <c r="B112" s="4" t="inlineStr">
         <is>
           <t>NotificationRepository#findByIdAndUserId / NotificationRepository#markAsRead / NotificationResponse#from</t>
         </is>
       </c>
-      <c r="C132" s="8" t="n"/>
-      <c r="D132" s="8" t="n"/>
-      <c r="E132" s="8" t="n"/>
-      <c r="F132" s="9" t="n"/>
-    </row>
-    <row r="133" ht="19" customHeight="1">
-      <c r="A133" s="10" t="inlineStr">
+      <c r="C112" s="8" t="n"/>
+      <c r="D112" s="8" t="n"/>
+      <c r="E112" s="8" t="n"/>
+      <c r="F112" s="9" t="n"/>
+    </row>
+    <row r="113" ht="19" customHeight="1">
+      <c r="A113" s="10" t="inlineStr">
         <is>
           <t>呼出元</t>
         </is>
       </c>
-      <c r="B133" s="4" t="inlineStr">
+      <c r="B113" s="4" t="inlineStr">
         <is>
           <t>NotificationController#markAsRead（ONL-019）</t>
         </is>
       </c>
-      <c r="C133" s="8" t="n"/>
-      <c r="D133" s="8" t="n"/>
-      <c r="E133" s="8" t="n"/>
-      <c r="F133" s="9" t="n"/>
-    </row>
-    <row r="134" ht="19" customHeight="1">
-      <c r="A134" s="10" t="inlineStr">
+      <c r="C113" s="8" t="n"/>
+      <c r="D113" s="8" t="n"/>
+      <c r="E113" s="8" t="n"/>
+      <c r="F113" s="9" t="n"/>
+    </row>
+    <row r="114" ht="19" customHeight="1">
+      <c r="A114" s="10" t="inlineStr">
         <is>
           <t>関連 ONL</t>
         </is>
       </c>
-      <c r="B134" s="4" t="inlineStr">
+      <c r="B114" s="4" t="inlineStr">
         <is>
           <t>ONL-019 通知一覧取得（API-019）</t>
         </is>
       </c>
-      <c r="C134" s="8" t="n"/>
-      <c r="D134" s="8" t="n"/>
-      <c r="E134" s="8" t="n"/>
-      <c r="F134" s="9" t="n"/>
-    </row>
-    <row r="135" ht="124" customHeight="1">
-      <c r="A135" s="10" t="inlineStr">
+      <c r="C114" s="8" t="n"/>
+      <c r="D114" s="8" t="n"/>
+      <c r="E114" s="8" t="n"/>
+      <c r="F114" s="9" t="n"/>
+    </row>
+    <row r="115" ht="124" customHeight="1">
+      <c r="A115" s="10" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="B135" s="4" t="inlineStr">
+      <c r="B115" s="4" t="inlineStr">
         <is>
           <t>【冪等】すでに既読ならエラーにせず、更新も行わずそのまま 200 で返す。
 【同時実行】2つのリクエストが同時に未読と判定しても、UPDATE は is_read = FALSE の行だけが対象なので、片方の更新件数が 0 になるだけで結果は同じ。更新件数 0 はエラーにしない。ロック・楽観ロックは不要。
@@ -8380,32 +8086,362 @@
 【画面遷移】応答の requestId が null でなければ、画面（SCR-101）は SCR-106 の該当申請へ遷移する。null（LEAVE_GRANTED / LEAVE_ALERT）は遷移しない。</t>
         </is>
       </c>
+      <c r="C115" s="8" t="n"/>
+      <c r="D115" s="8" t="n"/>
+      <c r="E115" s="8" t="n"/>
+      <c r="F115" s="9" t="n"/>
+    </row>
+    <row r="116" ht="19" customHeight="1">
+      <c r="A116" s="14" t="inlineStr">
+        <is>
+          <t>③-2-5  NotificationService#existsMonthly  （一覧 No. 5）</t>
+        </is>
+      </c>
+      <c r="B116" s="8" t="n"/>
+      <c r="C116" s="8" t="n"/>
+      <c r="D116" s="8" t="n"/>
+      <c r="E116" s="8" t="n"/>
+      <c r="F116" s="9" t="n"/>
+    </row>
+    <row r="117" ht="19" customHeight="1">
+      <c r="A117" s="10" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>Service（ONL-019 が追加。バッチの月次重複防止用）</t>
+        </is>
+      </c>
+      <c r="C117" s="8" t="n"/>
+      <c r="D117" s="8" t="n"/>
+      <c r="E117" s="8" t="n"/>
+      <c r="F117" s="9" t="n"/>
+    </row>
+    <row r="118" ht="34" customHeight="1">
+      <c r="A118" s="10" t="inlineStr">
+        <is>
+          <t>シグネチャ</t>
+        </is>
+      </c>
+      <c r="B118" s="15" t="inlineStr">
+        <is>
+          <t>@Transactional(readOnly = true)
+public boolean existsMonthly(Long userId, String type, YearMonth yearMonth)</t>
+        </is>
+      </c>
+      <c r="C118" s="8" t="n"/>
+      <c r="D118" s="8" t="n"/>
+      <c r="E118" s="8" t="n"/>
+      <c r="F118" s="9" t="n"/>
+    </row>
+    <row r="119" ht="34" customHeight="1">
+      <c r="A119" s="10" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>指定ユーザー・指定種別の通知が、指定した年月（JST）に既に作成されているかを返す。年5日取得義務アラート（BAT-002）が同じ月に二重通知しないために使う。</t>
+        </is>
+      </c>
+      <c r="C119" s="8" t="n"/>
+      <c r="D119" s="8" t="n"/>
+      <c r="E119" s="8" t="n"/>
+      <c r="F119" s="9" t="n"/>
+    </row>
+    <row r="120" ht="19" customHeight="1">
+      <c r="A120" s="10" t="inlineStr">
+        <is>
+          <t>アノテーション</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>@Transactional(readOnly = true)  ※クラスに @Service</t>
+        </is>
+      </c>
+      <c r="C120" s="8" t="n"/>
+      <c r="D120" s="8" t="n"/>
+      <c r="E120" s="8" t="n"/>
+      <c r="F120" s="9" t="n"/>
+    </row>
+    <row r="121" ht="19" customHeight="1">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>引数名</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="D121" s="8" t="n"/>
+      <c r="E121" s="8" t="n"/>
+      <c r="F121" s="9" t="n"/>
+    </row>
+    <row r="122" ht="19" customHeight="1">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>userId</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>通知先ユーザーID</t>
+        </is>
+      </c>
+      <c r="D122" s="8" t="n"/>
+      <c r="E122" s="8" t="n"/>
+      <c r="F122" s="9" t="n"/>
+    </row>
+    <row r="123" ht="19" customHeight="1">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>通知種別（NotificationType。BAT-002 は LEAVE_ALERT）</t>
+        </is>
+      </c>
+      <c r="D123" s="8" t="n"/>
+      <c r="E123" s="8" t="n"/>
+      <c r="F123" s="9" t="n"/>
+    </row>
+    <row r="124" ht="19" customHeight="1">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>yearMonth</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>YearMonth</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>確認する年月（JST の暦月）</t>
+        </is>
+      </c>
+      <c r="D124" s="8" t="n"/>
+      <c r="E124" s="8" t="n"/>
+      <c r="F124" s="9" t="n"/>
+    </row>
+    <row r="125" ht="19" customHeight="1">
+      <c r="A125" s="10" t="inlineStr">
+        <is>
+          <t>戻り値</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>boolean（1件以上あれば true）</t>
+        </is>
+      </c>
+      <c r="C125" s="8" t="n"/>
+      <c r="D125" s="8" t="n"/>
+      <c r="E125" s="8" t="n"/>
+      <c r="F125" s="9" t="n"/>
+    </row>
+    <row r="126" ht="19" customHeight="1">
+      <c r="A126" s="10" t="inlineStr">
+        <is>
+          <t>例外</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>なし（引数 null は NullPointerException＝呼出し側のバグ → E-012）</t>
+        </is>
+      </c>
+      <c r="C126" s="8" t="n"/>
+      <c r="D126" s="8" t="n"/>
+      <c r="E126" s="8" t="n"/>
+      <c r="F126" s="9" t="n"/>
+    </row>
+    <row r="127" ht="19" customHeight="1">
+      <c r="A127" s="10" t="inlineStr">
+        <is>
+          <t>トランザクション</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>@Transactional(readOnly = true)  ※クラスに @Service</t>
+        </is>
+      </c>
+      <c r="C127" s="8" t="n"/>
+      <c r="D127" s="8" t="n"/>
+      <c r="E127" s="8" t="n"/>
+      <c r="F127" s="9" t="n"/>
+    </row>
+    <row r="128" ht="64" customHeight="1">
+      <c r="A128" s="10" t="inlineStr">
+        <is>
+          <t>処理詳細（疑似コード）</t>
+        </is>
+      </c>
+      <c r="B128" s="15" t="inlineStr">
+        <is>
+          <t>LocalDateTime from = yearMonth.atDay(1).atStartOfDay();            // 当月 1 日 00:00:00（JST）
+LocalDateTime to   = yearMonth.plusMonths(1).atDay(1).atStartOfDay();   // 翌月 1 日 00:00:00（含まない）
+return notificationRepository
+    .existsByUserIdAndTypeAndCreatedAtGreaterThanEqualAndCreatedAtLessThan(userId, type, from, to);</t>
+        </is>
+      </c>
+      <c r="C128" s="8" t="n"/>
+      <c r="D128" s="8" t="n"/>
+      <c r="E128" s="8" t="n"/>
+      <c r="F128" s="9" t="n"/>
+    </row>
+    <row r="129" ht="19" customHeight="1">
+      <c r="A129" s="10" t="inlineStr">
+        <is>
+          <t>呼出先</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>NotificationRepository#existsByUserIdAndTypeAndCreatedAtGreaterThanEqualAndCreatedAtLessThan</t>
+        </is>
+      </c>
+      <c r="C129" s="8" t="n"/>
+      <c r="D129" s="8" t="n"/>
+      <c r="E129" s="8" t="n"/>
+      <c r="F129" s="9" t="n"/>
+    </row>
+    <row r="130" ht="34" customHeight="1">
+      <c r="A130" s="10" t="inlineStr">
+        <is>
+          <t>呼出元</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>MandatoryLeaveAlertUnitService#alertOne（BAT-002）
+NotificationService#existsMonthly（4引数 overload）/ existsBy…MessageStartingWith…（BAT-002）</t>
+        </is>
+      </c>
+      <c r="C130" s="8" t="n"/>
+      <c r="D130" s="8" t="n"/>
+      <c r="E130" s="8" t="n"/>
+      <c r="F130" s="9" t="n"/>
+    </row>
+    <row r="131" ht="19" customHeight="1">
+      <c r="A131" s="10" t="inlineStr">
+        <is>
+          <t>関連 ONL</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>ONL-019 通知一覧取得（API-019）</t>
+        </is>
+      </c>
+      <c r="C131" s="8" t="n"/>
+      <c r="D131" s="8" t="n"/>
+      <c r="E131" s="8" t="n"/>
+      <c r="F131" s="9" t="n"/>
+    </row>
+    <row r="132" ht="64" customHeight="1">
+      <c r="A132" s="10" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>created_at は DB の DEFAULT CURRENT_TIMESTAMP（接続の TimeZone は Asia/Tokyo。7.3 設定値）のため、JST の暦月で判定できる。
+呼出し元の例（BAT-002）: if (!notificationService.existsMonthly(userId, NotificationType.LEAVE_ALERT, YearMonth.from(today))) notificationService.notify(userId, NotificationType.LEAVE_ALERT, msg, null);
+既読・未読は問わない。ユーザー単位で判定する（他ユーザーの通知は影響しない）。</t>
+        </is>
+      </c>
+      <c r="C132" s="8" t="n"/>
+      <c r="D132" s="8" t="n"/>
+      <c r="E132" s="8" t="n"/>
+      <c r="F132" s="9" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t>④ クラス不変条件・排他・留意点</t>
+        </is>
+      </c>
+      <c r="B134" s="8" t="n"/>
+      <c r="C134" s="8" t="n"/>
+      <c r="D134" s="8" t="n"/>
+      <c r="E134" s="8" t="n"/>
+      <c r="F134" s="9" t="n"/>
+    </row>
+    <row r="135" ht="64" customHeight="1">
+      <c r="A135" s="10" t="inlineStr">
+        <is>
+          <t>トランザクション境界</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>@Transactional(propagation = REQUIRED)  ※呼出し元のトランザクションに参加する（REQUIRES_NEW にしない）  ← notify
+@Transactional(readOnly = true)  ※クラスに @Service  ← getNotifications, existsMonthly
+@Transactional  ※クラスに @Service。DB 更新を伴うため readOnly にしない  ← markAsRead
+@Transactional(readOnly = true)（Service）  ← existsMonthly</t>
+        </is>
+      </c>
       <c r="C135" s="8" t="n"/>
       <c r="D135" s="8" t="n"/>
       <c r="E135" s="8" t="n"/>
       <c r="F135" s="9" t="n"/>
     </row>
-    <row r="136" ht="19" customHeight="1">
-      <c r="A136" s="14" t="inlineStr">
-        <is>
-          <t>③-2-6  NotificationService#existsMonthly  （一覧 No. 6）</t>
-        </is>
-      </c>
-      <c r="B136" s="8" t="n"/>
+    <row r="136" ht="34" customHeight="1">
+      <c r="A136" s="10" t="inlineStr">
+        <is>
+          <t>送出するエラーコード</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>E-010（HTTP 403）: markAsRead
+E-012（HTTP 500）: existsMonthly, notify</t>
+        </is>
+      </c>
       <c r="C136" s="8" t="n"/>
       <c r="D136" s="8" t="n"/>
       <c r="E136" s="8" t="n"/>
       <c r="F136" s="9" t="n"/>
     </row>
-    <row r="137" ht="19" customHeight="1">
+    <row r="137" ht="64" customHeight="1">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>種別</t>
+          <t>設計原則（このクラス種別）</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Service（ONL-019 が追加。バッチの月次重複防止用）</t>
+          <t>・コンストラクタ注入のみ（フィールド注入禁止）。
+・Entity を返さず DTO に変換して返す（例外：他 Service 向けの公開メソッドは Entity / 数値を返してよい）。
+・業務エラーは BusinessException(code, message, HttpStatus) で送出し、Controller 層に判断を残さない。
+・日時は Clock（Asia/Tokyo）から取得し、LocalDate.now() をそのまま使わない（テスト容易性）。</t>
         </is>
       </c>
       <c r="C137" s="8" t="n"/>
@@ -8413,50 +8449,25 @@
       <c r="E137" s="8" t="n"/>
       <c r="F137" s="9" t="n"/>
     </row>
-    <row r="138" ht="34" customHeight="1">
-      <c r="A138" s="10" t="inlineStr">
-        <is>
-          <t>シグネチャ</t>
-        </is>
-      </c>
-      <c r="B138" s="15" t="inlineStr">
-        <is>
-          <t>@Transactional(readOnly = true)
-public boolean existsMonthly(Long userId, String type, YearMonth yearMonth)</t>
-        </is>
-      </c>
-      <c r="C138" s="8" t="n"/>
-      <c r="D138" s="8" t="n"/>
-      <c r="E138" s="8" t="n"/>
-      <c r="F138" s="9" t="n"/>
-    </row>
-    <row r="139" ht="34" customHeight="1">
-      <c r="A139" s="10" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="B139" s="4" t="inlineStr">
-        <is>
-          <t>指定ユーザー・指定種別の通知が、指定した年月（JST）に既に作成されているかを返す。年5日取得義務アラート（BAT-002）が同じ月に二重通知しないために使う。</t>
-        </is>
-      </c>
+    <row r="139">
+      <c r="A139" s="7" t="inlineStr">
+        <is>
+          <t>⑤ 付帯情報（ONL の補足表・定義コード）</t>
+        </is>
+      </c>
+      <c r="B139" s="8" t="n"/>
       <c r="C139" s="8" t="n"/>
       <c r="D139" s="8" t="n"/>
       <c r="E139" s="8" t="n"/>
       <c r="F139" s="9" t="n"/>
     </row>
     <row r="140" ht="19" customHeight="1">
-      <c r="A140" s="10" t="inlineStr">
-        <is>
-          <t>アノテーション</t>
-        </is>
-      </c>
-      <c r="B140" s="4" t="inlineStr">
-        <is>
-          <t>@Transactional(readOnly = true)  ※クラスに @Service</t>
-        </is>
-      </c>
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>ONL-005 通知の呼び出し仕様（NotificationService#notify は本書が定義元。ONL-019 は参照）</t>
+        </is>
+      </c>
+      <c r="B140" s="8" t="n"/>
       <c r="C140" s="8" t="n"/>
       <c r="D140" s="8" t="n"/>
       <c r="E140" s="8" t="n"/>
@@ -8465,39 +8476,31 @@
     <row r="141" ht="19" customHeight="1">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>引数名</t>
+          <t>項目</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="C141" s="6" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
+          <t>値</t>
+        </is>
+      </c>
+      <c r="C141" s="8" t="n"/>
       <c r="D141" s="8" t="n"/>
       <c r="E141" s="8" t="n"/>
       <c r="F141" s="9" t="n"/>
     </row>
-    <row r="142" ht="19" customHeight="1">
+    <row r="142" ht="34" customHeight="1">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>userId</t>
+          <t>シグネチャ</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="C142" s="4" t="inlineStr">
-        <is>
-          <t>通知先ユーザーID</t>
-        </is>
-      </c>
+          <t>notify(Long userId, String type, String message, Long requestId)  ※全 ONL で同一。疑似コードは 6.x NotificationService#notify に完全記載</t>
+        </is>
+      </c>
+      <c r="C142" s="8" t="n"/>
       <c r="D142" s="8" t="n"/>
       <c r="E142" s="8" t="n"/>
       <c r="F142" s="9" t="n"/>
@@ -8510,14 +8513,10 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="C143" s="4" t="inlineStr">
-        <is>
-          <t>通知種別（NotificationType。BAT-002 は LEAVE_ALERT）</t>
-        </is>
-      </c>
+          <t>NotificationType.REQUEST_SUBMITTED（承認依頼）。種別の全7値は 6.x 定数クラスを参照</t>
+        </is>
+      </c>
+      <c r="C143" s="8" t="n"/>
       <c r="D143" s="8" t="n"/>
       <c r="E143" s="8" t="n"/>
       <c r="F143" s="9" t="n"/>
@@ -8525,32 +8524,28 @@
     <row r="144" ht="19" customHeight="1">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>yearMonth</t>
+          <t>userId</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>YearMonth</t>
-        </is>
-      </c>
-      <c r="C144" s="4" t="inlineStr">
-        <is>
-          <t>確認する年月（JST の暦月）</t>
-        </is>
-      </c>
+          <t>resolveCurrentApproverIds の戻り値の各ユーザー（1段目の上長、または有効な全管理者）</t>
+        </is>
+      </c>
+      <c r="C144" s="8" t="n"/>
       <c r="D144" s="8" t="n"/>
       <c r="E144" s="8" t="n"/>
       <c r="F144" s="9" t="n"/>
     </row>
     <row r="145" ht="19" customHeight="1">
-      <c r="A145" s="10" t="inlineStr">
-        <is>
-          <t>戻り値</t>
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>requestId</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>boolean（1件以上あれば true）</t>
+          <t>登録した申請の ID（r.getId()）。画面は requestId があれば SCR-106 の該当申請へ遷移する</t>
         </is>
       </c>
       <c r="C145" s="8" t="n"/>
@@ -8559,14 +8554,14 @@
       <c r="F145" s="9" t="n"/>
     </row>
     <row r="146" ht="19" customHeight="1">
-      <c r="A146" s="10" t="inlineStr">
-        <is>
-          <t>例外</t>
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>message</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>なし（引数 null は NullPointerException＝呼出し側のバグ → E-012）</t>
+          <t>buildSubmittedMessage の文面（例: 山田 太郎さんから休暇申請（年次有給休暇 2026-10-14〜2026-10-16）が提出されました。）</t>
         </is>
       </c>
       <c r="C146" s="8" t="n"/>
@@ -8574,15 +8569,15 @@
       <c r="E146" s="8" t="n"/>
       <c r="F146" s="9" t="n"/>
     </row>
-    <row r="147" ht="19" customHeight="1">
-      <c r="A147" s="10" t="inlineStr">
-        <is>
-          <t>トランザクション</t>
+    <row r="147" ht="34" customHeight="1">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>注意</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>@Transactional(readOnly = true)  ※クラスに @Service</t>
+          <t>notifications には type / request_id 列がある（schema.sql）。本処理は同一トランザクションで呼ぶ（REQUIRED）。requests の INSERT 後に呼ぶこと（FK）</t>
         </is>
       </c>
       <c r="C147" s="8" t="n"/>
@@ -8590,152 +8585,179 @@
       <c r="E147" s="8" t="n"/>
       <c r="F147" s="9" t="n"/>
     </row>
-    <row r="148" ht="64" customHeight="1">
-      <c r="A148" s="10" t="inlineStr">
-        <is>
-          <t>処理詳細（疑似コード）</t>
-        </is>
-      </c>
-      <c r="B148" s="15" t="inlineStr">
-        <is>
-          <t>LocalDateTime from = yearMonth.atDay(1).atStartOfDay();            // 当月 1 日 00:00:00（JST）
-LocalDateTime to   = yearMonth.plusMonths(1).atDay(1).atStartOfDay();   // 翌月 1 日 00:00:00（含まない）
-return notificationRepository
-    .existsByUserIdAndTypeAndCreatedAtGreaterThanEqualAndCreatedAtLessThan(userId, type, from, to);</t>
-        </is>
-      </c>
+    <row r="148" ht="19" customHeight="1">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
+          <t>ONL-019 POST /api/notifications/{id}/read の処理手順</t>
+        </is>
+      </c>
+      <c r="B148" s="8" t="n"/>
       <c r="C148" s="8" t="n"/>
       <c r="D148" s="8" t="n"/>
       <c r="E148" s="8" t="n"/>
       <c r="F148" s="9" t="n"/>
     </row>
     <row r="149" ht="19" customHeight="1">
-      <c r="A149" s="10" t="inlineStr">
-        <is>
-          <t>呼出先</t>
-        </is>
-      </c>
-      <c r="B149" s="4" t="inlineStr">
-        <is>
-          <t>NotificationRepository#existsByUserIdAndTypeAndCreatedAtGreaterThanEqualAndCreatedAtLessThan</t>
-        </is>
-      </c>
-      <c r="C149" s="8" t="n"/>
+      <c r="A149" s="6" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B149" s="6" t="inlineStr">
+        <is>
+          <t>処理</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>詳細</t>
+        </is>
+      </c>
       <c r="D149" s="8" t="n"/>
       <c r="E149" s="8" t="n"/>
       <c r="F149" s="9" t="n"/>
     </row>
-    <row r="150" ht="34" customHeight="1">
-      <c r="A150" s="10" t="inlineStr">
-        <is>
-          <t>呼出元</t>
+    <row r="150" ht="19" customHeight="1">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>①</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>MandatoryLeaveAlertUnitService#alertOne（BAT-002）
-NotificationService#existsMonthly（4引数 overload）/ existsBy…MessageStartingWith…（BAT-002）</t>
-        </is>
-      </c>
-      <c r="C150" s="8" t="n"/>
+          <t>JWT の検証</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>SecurityFilterChain。なし・不正・期限切れ → 401 / E-001（AuthenticationEntryPoint の JSON）</t>
+        </is>
+      </c>
       <c r="D150" s="8" t="n"/>
       <c r="E150" s="8" t="n"/>
       <c r="F150" s="9" t="n"/>
     </row>
-    <row r="151" ht="19" customHeight="1">
-      <c r="A151" s="10" t="inlineStr">
-        <is>
-          <t>関連 ONL</t>
+    <row r="151" ht="34" customHeight="1">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>②</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>ONL-019 通知一覧取得（API-019）</t>
-        </is>
-      </c>
-      <c r="C151" s="8" t="n"/>
+          <t>ログインユーザーID の取得</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>Controller: Long.valueOf(auth.getName())</t>
+        </is>
+      </c>
       <c r="D151" s="8" t="n"/>
       <c r="E151" s="8" t="n"/>
       <c r="F151" s="9" t="n"/>
     </row>
-    <row r="152" ht="64" customHeight="1">
-      <c r="A152" s="10" t="inlineStr">
-        <is>
-          <t>備考</t>
+    <row r="152" ht="19" customHeight="1">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>③</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>created_at は DB の DEFAULT CURRENT_TIMESTAMP（接続の TimeZone は Asia/Tokyo。7.3 設定値）のため、JST の暦月で判定できる。
-呼出し元の例（BAT-002）: if (!notificationService.existsMonthly(userId, NotificationType.LEAVE_ALERT, YearMonth.from(today))) notificationService.notify(userId, NotificationType.LEAVE_ALERT, msg, null);
-既読・未読は問わない。ユーザー単位で判定する（他ユーザーの通知は影響しない）。</t>
-        </is>
-      </c>
-      <c r="C152" s="8" t="n"/>
+          <t>本人の通知を検索</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>notificationRepository.findByIdAndUserId(id, userId)。該当なし（存在しない／他人の通知）→ E-010 / HTTP 403</t>
+        </is>
+      </c>
       <c r="D152" s="8" t="n"/>
       <c r="E152" s="8" t="n"/>
       <c r="F152" s="9" t="n"/>
     </row>
-    <row r="154">
-      <c r="A154" s="7" t="inlineStr">
-        <is>
-          <t>④ クラス不変条件・排他・留意点</t>
-        </is>
-      </c>
-      <c r="B154" s="8" t="n"/>
-      <c r="C154" s="8" t="n"/>
+    <row r="153" ht="19" customHeight="1">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>既読か？</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>n.isRead() が true → 更新せず ⑥ へ（冪等・エラーにしない）</t>
+        </is>
+      </c>
+      <c r="D153" s="8" t="n"/>
+      <c r="E153" s="8" t="n"/>
+      <c r="F153" s="9" t="n"/>
+    </row>
+    <row r="154" ht="19" customHeight="1">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>既読化 UPDATE</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>markAsRead(id, userId)（updated_at は DB トリガ）。更新件数 0 でもエラーにしない</t>
+        </is>
+      </c>
       <c r="D154" s="8" t="n"/>
       <c r="E154" s="8" t="n"/>
       <c r="F154" s="9" t="n"/>
     </row>
-    <row r="155" ht="79" customHeight="1">
-      <c r="A155" s="10" t="inlineStr">
-        <is>
-          <t>トランザクション境界</t>
+    <row r="155" ht="19" customHeight="1">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>⑥</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>@Transactional(propagation = REQUIRED)  ※呼出し元のトランザクションに参加する（REQUIRES_NEW にしない）  ← notify
-@Transactional(readOnly = true)  ※クラスに @Service  ← getNotifications, existsMonthly
-@Transactional  ※クラスに @Service。DB 更新を伴うため readOnly にしない  ← markAsRead
-@Transactional(readOnly = true)（Service）  ← existsByUserIdAndTypeAndMessageStartingWithAndCreatedAtGreaterThanEqualAndCreatedAtLessThan</t>
-        </is>
-      </c>
-      <c r="C155" s="8" t="n"/>
+          <t>レスポンス返却</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>NotificationResponse.from(n)（isRead = true）を HTTP 200 で返す</t>
+        </is>
+      </c>
       <c r="D155" s="8" t="n"/>
       <c r="E155" s="8" t="n"/>
       <c r="F155" s="9" t="n"/>
     </row>
-    <row r="156" ht="34" customHeight="1">
-      <c r="A156" s="10" t="inlineStr">
-        <is>
-          <t>送出するエラーコード</t>
-        </is>
-      </c>
-      <c r="B156" s="4" t="inlineStr">
-        <is>
-          <t>E-010（HTTP 403）: markAsRead
-E-012（HTTP 500）: existsMonthly, notify</t>
-        </is>
-      </c>
+    <row r="156" ht="19" customHeight="1">
+      <c r="A156" s="6" t="inlineStr">
+        <is>
+          <t>ONL-019 NotificationService#notify（参照のみ・ONL-005 が定義元。他処理が通知を作成するときの契約）</t>
+        </is>
+      </c>
+      <c r="B156" s="8" t="n"/>
       <c r="C156" s="8" t="n"/>
       <c r="D156" s="8" t="n"/>
       <c r="E156" s="8" t="n"/>
       <c r="F156" s="9" t="n"/>
     </row>
-    <row r="157" ht="64" customHeight="1">
-      <c r="A157" s="10" t="inlineStr">
-        <is>
-          <t>設計原則（このクラス種別）</t>
-        </is>
-      </c>
-      <c r="B157" s="4" t="inlineStr">
-        <is>
-          <t>・コンストラクタ注入のみ（フィールド注入禁止）。
-・Entity を返さず DTO に変換して返す（例外：他 Service 向けの公開メソッドは Entity / 数値を返してよい）。
-・業務エラーは BusinessException(code, message, HttpStatus) で送出し、Controller 層に判断を残さない。
-・日時は Clock（Asia/Tokyo）から取得し、LocalDate.now() をそのまま使わない（テスト容易性）。</t>
+    <row r="157" ht="19" customHeight="1">
+      <c r="A157" s="6" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B157" s="6" t="inlineStr">
+        <is>
+          <t>内容</t>
         </is>
       </c>
       <c r="C157" s="8" t="n"/>
@@ -8743,39 +8765,63 @@
       <c r="E157" s="8" t="n"/>
       <c r="F157" s="9" t="n"/>
     </row>
-    <row r="159">
-      <c r="A159" s="7" t="inlineStr">
-        <is>
-          <t>⑤ 付帯情報（ONL の補足表・定義コード）</t>
-        </is>
-      </c>
-      <c r="B159" s="8" t="n"/>
+    <row r="158" ht="34" customHeight="1">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t>シグネチャ</t>
+        </is>
+      </c>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
+          <t>public void notify(Long userId, String type, String message, Long requestId)  ※完全な疑似コードは ONL-005 の NotificationService#notify</t>
+        </is>
+      </c>
+      <c r="C158" s="8" t="n"/>
+      <c r="D158" s="8" t="n"/>
+      <c r="E158" s="8" t="n"/>
+      <c r="F158" s="9" t="n"/>
+    </row>
+    <row r="159" ht="34" customHeight="1">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>定義元</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>ONL-005（最初の利用者）が notify・NotificationRepository・Notification Entity・NotificationType を定義。本処理（ONL-019）は一覧取得・既読化・existsMonthly のみを追加する</t>
+        </is>
+      </c>
       <c r="C159" s="8" t="n"/>
       <c r="D159" s="8" t="n"/>
       <c r="E159" s="8" t="n"/>
       <c r="F159" s="9" t="n"/>
     </row>
-    <row r="160" ht="19" customHeight="1">
-      <c r="A160" s="6" t="inlineStr">
-        <is>
-          <t>ONL-005 通知の呼び出し仕様（NotificationService#notify は本書が定義元。ONL-019 は参照）</t>
-        </is>
-      </c>
-      <c r="B160" s="8" t="n"/>
+    <row r="160" ht="34" customHeight="1">
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t>保存内容</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>INSERT INTO notifications (user_id, type, request_id, message, is_read) VALUES (?, ?, ?, ?, FALSE)。created_at / updated_at は DB の DEFAULT CURRENT_TIMESTAMP（DB セッションが JST であること。7.3 参照）</t>
+        </is>
+      </c>
       <c r="C160" s="8" t="n"/>
       <c r="D160" s="8" t="n"/>
       <c r="E160" s="8" t="n"/>
       <c r="F160" s="9" t="n"/>
     </row>
-    <row r="161" ht="19" customHeight="1">
-      <c r="A161" s="6" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B161" s="6" t="inlineStr">
-        <is>
-          <t>値</t>
+    <row r="161" ht="49" customHeight="1">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>type / requestId</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>type は NotificationType の7値（REQUEST_SUBMITTED / REQUEST_APPROVED / REQUEST_RETURNED / REQUEST_REJECTED / REQUEST_WITHDRAWN / LEAVE_GRANTED / LEAVE_ALERT）。requestId は REQUEST_* で必須、LEAVE_* は null。SCR-101『通知を選択 → 関連する申請へ遷移』は requestId があれば SCR-106 の該当申請へ遷移することで実現する（旧『SCR-106 で代替』の記述は廃止）</t>
         </is>
       </c>
       <c r="C161" s="8" t="n"/>
@@ -8783,15 +8829,15 @@
       <c r="E161" s="8" t="n"/>
       <c r="F161" s="9" t="n"/>
     </row>
-    <row r="162" ht="34" customHeight="1">
+    <row r="162" ht="19" customHeight="1">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>シグネチャ</t>
+          <t>message の長さ</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>notify(Long userId, String type, String message, Long requestId)  ※全 ONL で同一。疑似コードは 6.x NotificationService#notify に完全記載</t>
+          <t>VARCHAR(500)。500 文字を超える場合は notify 内で切り詰める（DB 制約違反の防止）</t>
         </is>
       </c>
       <c r="C162" s="8" t="n"/>
@@ -8802,12 +8848,12 @@
     <row r="163" ht="19" customHeight="1">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>トランザクション</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>NotificationType.REQUEST_SUBMITTED（承認依頼）。種別の全7値は 6.x 定数クラスを参照</t>
+          <t>呼び出し元の @Transactional に参加（REQUIRED）。通知の登録に失敗した場合は業務処理ごとロールバックされる</t>
         </is>
       </c>
       <c r="C163" s="8" t="n"/>
@@ -8816,30 +8862,26 @@
       <c r="F163" s="9" t="n"/>
     </row>
     <row r="164" ht="19" customHeight="1">
-      <c r="A164" s="4" t="inlineStr">
-        <is>
-          <t>userId</t>
-        </is>
-      </c>
-      <c r="B164" s="4" t="inlineStr">
-        <is>
-          <t>resolveCurrentApproverIds の戻り値の各ユーザー（1段目の上長、または有効な全管理者）</t>
-        </is>
-      </c>
+      <c r="A164" s="6" t="inlineStr">
+        <is>
+          <t>ONL-019 existsMonthly の呼出し元（参照）</t>
+        </is>
+      </c>
+      <c r="B164" s="8" t="n"/>
       <c r="C164" s="8" t="n"/>
       <c r="D164" s="8" t="n"/>
       <c r="E164" s="8" t="n"/>
       <c r="F164" s="9" t="n"/>
     </row>
     <row r="165" ht="19" customHeight="1">
-      <c r="A165" s="4" t="inlineStr">
-        <is>
-          <t>requestId</t>
-        </is>
-      </c>
-      <c r="B165" s="4" t="inlineStr">
-        <is>
-          <t>登録した申請の ID（r.getId()）。画面は requestId があれば SCR-106 の該当申請へ遷移する</t>
+      <c r="A165" s="6" t="inlineStr">
+        <is>
+          <t>呼出し元</t>
+        </is>
+      </c>
+      <c r="B165" s="6" t="inlineStr">
+        <is>
+          <t>用途</t>
         </is>
       </c>
       <c r="C165" s="8" t="n"/>
@@ -8847,15 +8889,15 @@
       <c r="E165" s="8" t="n"/>
       <c r="F165" s="9" t="n"/>
     </row>
-    <row r="166" ht="19" customHeight="1">
+    <row r="166" ht="49" customHeight="1">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>BAT-002（年5日取得義務アラート）</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>buildSubmittedMessage の文面（例: 山田 太郎さんから休暇申請（年次有給休暇 2026-10-14〜2026-10-16）が提出されました。）</t>
+          <t>宛先ごとに existsMonthly(宛先, LEAVE_ALERT, 先頭キー『[対象者ID:{id} 付与日:{yyyy-MM-dd}]』, 当月)（4 引数 overload）が false のときだけ notify する（同月・同一対象者・同一付与日で1回まで）。対象行の抽出は ONL-013 の LeaveBalanceService#findAlertBaseRows。3 引数版は対象者を区別できないため BAT-002 では使わない</t>
         </is>
       </c>
       <c r="C166" s="8" t="n"/>
@@ -8863,26 +8905,10 @@
       <c r="E166" s="8" t="n"/>
       <c r="F166" s="9" t="n"/>
     </row>
-    <row r="167" ht="34" customHeight="1">
-      <c r="A167" s="4" t="inlineStr">
-        <is>
-          <t>注意</t>
-        </is>
-      </c>
-      <c r="B167" s="4" t="inlineStr">
-        <is>
-          <t>notifications には type / request_id 列がある（schema.sql）。本処理は同一トランザクションで呼ぶ（REQUIRED）。requests の INSERT 後に呼ぶこと（FK）</t>
-        </is>
-      </c>
-      <c r="C167" s="8" t="n"/>
-      <c r="D167" s="8" t="n"/>
-      <c r="E167" s="8" t="n"/>
-      <c r="F167" s="9" t="n"/>
-    </row>
-    <row r="168" ht="19" customHeight="1">
-      <c r="A168" s="6" t="inlineStr">
-        <is>
-          <t>ONL-019 POST /api/notifications/{id}/read の処理手順</t>
+    <row r="168">
+      <c r="A168" s="7" t="inlineStr">
+        <is>
+          <t>⑥ 単体テスト観点（関連 ONL の tests を引用）</t>
         </is>
       </c>
       <c r="B168" s="8" t="n"/>
@@ -8894,262 +8920,366 @@
     <row r="169" ht="19" customHeight="1">
       <c r="A169" s="6" t="inlineStr">
         <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B169" s="6" t="inlineStr">
-        <is>
-          <t>処理</t>
-        </is>
-      </c>
-      <c r="C169" s="6" t="inlineStr">
-        <is>
-          <t>詳細</t>
-        </is>
-      </c>
+          <t>ONL-005: NotificationService#notify（Mockito / @DataJpaTest）</t>
+        </is>
+      </c>
+      <c r="B169" s="8" t="n"/>
+      <c r="C169" s="8" t="n"/>
       <c r="D169" s="8" t="n"/>
       <c r="E169" s="8" t="n"/>
       <c r="F169" s="9" t="n"/>
     </row>
     <row r="170" ht="19" customHeight="1">
-      <c r="A170" s="4" t="inlineStr">
-        <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="B170" s="4" t="inlineStr">
-        <is>
-          <t>JWT の検証</t>
-        </is>
-      </c>
-      <c r="C170" s="4" t="inlineStr">
-        <is>
-          <t>SecurityFilterChain。なし・不正・期限切れ → 401 / E-001（AuthenticationEntryPoint の JSON）</t>
-        </is>
-      </c>
-      <c r="D170" s="8" t="n"/>
-      <c r="E170" s="8" t="n"/>
-      <c r="F170" s="9" t="n"/>
-    </row>
-    <row r="171" ht="34" customHeight="1">
+      <c r="A170" s="6" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B170" s="6" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C170" s="6" t="inlineStr">
+        <is>
+          <t>観点・条件</t>
+        </is>
+      </c>
+      <c r="D170" s="9" t="n"/>
+      <c r="E170" s="6" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="F170" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="64" customHeight="1">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>ログインユーザーID の取得</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Controller: Long.valueOf(jwt.getSubject())</t>
-        </is>
-      </c>
-      <c r="D171" s="8" t="n"/>
-      <c r="E171" s="8" t="n"/>
-      <c r="F171" s="9" t="n"/>
-    </row>
-    <row r="172" ht="19" customHeight="1">
+          <t>type=REQUEST_SUBMITTED・requestId=15・message あり</t>
+        </is>
+      </c>
+      <c r="D171" s="9" t="n"/>
+      <c r="E171" s="4" t="inlineStr">
+        <is>
+          <t>Notification が save され、userId / type / requestId / message が入力どおり、read=false</t>
+        </is>
+      </c>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>INSERT 列は user_id, type, request_id, message, is_read</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="34" customHeight="1">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>③</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>本人の通知を検索</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>notificationRepository.findByIdAndUserId(id, userId)。該当なし（存在しない／他人の通知）→ E-010 / HTTP 403</t>
-        </is>
-      </c>
-      <c r="D172" s="8" t="n"/>
-      <c r="E172" s="8" t="n"/>
-      <c r="F172" s="9" t="n"/>
-    </row>
-    <row r="173" ht="19" customHeight="1">
+          <t>type=LEAVE_GRANTED・requestId=null</t>
+        </is>
+      </c>
+      <c r="D172" s="9" t="n"/>
+      <c r="E172" s="4" t="inlineStr">
+        <is>
+          <t>requestId=null で登録できる</t>
+        </is>
+      </c>
+      <c r="F172" s="4" t="inlineStr">
+        <is>
+          <t>LEAVE_* は申請に紐づかない</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="64" customHeight="1">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>④</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>既読か？</t>
+          <t>境界</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>n.isRead() が true → 更新せず ⑥ へ（冪等・エラーにしない）</t>
-        </is>
-      </c>
-      <c r="D173" s="8" t="n"/>
-      <c r="E173" s="8" t="n"/>
-      <c r="F173" s="9" t="n"/>
-    </row>
-    <row r="174" ht="19" customHeight="1">
+          <t>message が500文字／501文字（サロゲートペアを含む場合も）</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="n"/>
+      <c r="E173" s="4" t="inlineStr">
+        <is>
+          <t>500文字はそのまま。501文字は500文字（末尾「…」）に切り詰め、DB 制約違反にならない</t>
+        </is>
+      </c>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>コードポイント単位</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="34" customHeight="1">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>⑤</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>既読化 UPDATE</t>
+          <t>異常</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>markAsRead(id, userId)（updated_at は DB トリガ）。更新件数 0 でもエラーにしない</t>
-        </is>
-      </c>
-      <c r="D174" s="8" t="n"/>
-      <c r="E174" s="8" t="n"/>
-      <c r="F174" s="9" t="n"/>
-    </row>
-    <row r="175" ht="19" customHeight="1">
+          <t>userId = null／type = null／未知の type／message が空白のみ</t>
+        </is>
+      </c>
+      <c r="D174" s="9" t="n"/>
+      <c r="E174" s="4" t="inlineStr">
+        <is>
+          <t>IllegalArgumentException。save は呼ばれない</t>
+        </is>
+      </c>
+      <c r="F174" s="4" t="inlineStr">
+        <is>
+          <t>呼出し側のバグ（API では E-012）</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="34" customHeight="1">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>⑥</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>レスポンス返却</t>
+          <t>異常</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>NotificationResponse.from(n)（isRead = true）を HTTP 200 で返す</t>
-        </is>
-      </c>
-      <c r="D175" s="8" t="n"/>
-      <c r="E175" s="8" t="n"/>
-      <c r="F175" s="9" t="n"/>
-    </row>
-    <row r="176" ht="19" customHeight="1">
-      <c r="A176" s="6" t="inlineStr">
-        <is>
-          <t>ONL-019 NotificationService#notify（参照のみ・ONL-005 が定義元。他処理が通知を作成するときの契約）</t>
-        </is>
-      </c>
-      <c r="B176" s="8" t="n"/>
-      <c r="C176" s="8" t="n"/>
-      <c r="D176" s="8" t="n"/>
-      <c r="E176" s="8" t="n"/>
-      <c r="F176" s="9" t="n"/>
+          <t>type=REQUEST_APPROVED で requestId = null</t>
+        </is>
+      </c>
+      <c r="D175" s="9" t="n"/>
+      <c r="E175" s="4" t="inlineStr">
+        <is>
+          <t>IllegalArgumentException</t>
+        </is>
+      </c>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>REQUEST_BOUND は requestId 必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="49" customHeight="1">
+      <c r="A176" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t>存在しない requestId（@DataJpaTest）</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="n"/>
+      <c r="E176" s="4" t="inlineStr">
+        <is>
+          <t>DataIntegrityViolationException（fk_notifications_request_id）</t>
+        </is>
+      </c>
+      <c r="F176" s="4" t="inlineStr">
+        <is>
+          <t>requests の INSERT 後に呼ぶ前提の確認</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="19" customHeight="1">
       <c r="A177" s="6" t="inlineStr">
         <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B177" s="6" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
+          <t>ONL-019: NotificationService#getNotifications（Mockito）</t>
+        </is>
+      </c>
+      <c r="B177" s="8" t="n"/>
       <c r="C177" s="8" t="n"/>
       <c r="D177" s="8" t="n"/>
       <c r="E177" s="8" t="n"/>
       <c r="F177" s="9" t="n"/>
     </row>
-    <row r="178" ht="34" customHeight="1">
-      <c r="A178" s="4" t="inlineStr">
-        <is>
-          <t>シグネチャ</t>
-        </is>
-      </c>
-      <c r="B178" s="4" t="inlineStr">
-        <is>
-          <t>public void notify(Long userId, String type, String message, Long requestId)  ※完全な疑似コードは ONL-005 の NotificationService#notify</t>
-        </is>
-      </c>
-      <c r="C178" s="8" t="n"/>
-      <c r="D178" s="8" t="n"/>
-      <c r="E178" s="8" t="n"/>
-      <c r="F178" s="9" t="n"/>
-    </row>
-    <row r="179" ht="34" customHeight="1">
+    <row r="178" ht="19" customHeight="1">
+      <c r="A178" s="6" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B178" s="6" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C178" s="6" t="inlineStr">
+        <is>
+          <t>観点・条件</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="n"/>
+      <c r="E178" s="6" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="F178" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="49" customHeight="1">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>定義元</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>ONL-005（最初の利用者）が notify・NotificationRepository・Notification Entity・NotificationType を定義。本処理（ONL-019）は一覧取得・既読化・existsMonthly のみを追加する</t>
-        </is>
-      </c>
-      <c r="C179" s="8" t="n"/>
-      <c r="D179" s="8" t="n"/>
-      <c r="E179" s="8" t="n"/>
-      <c r="F179" s="9" t="n"/>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>Repository が3件（新しい順）を返す</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="n"/>
+      <c r="E179" s="4" t="inlineStr">
+        <is>
+          <t>notifications が同じ順で3件。isRead が Entity の値どおり</t>
+        </is>
+      </c>
+      <c r="F179" s="4" t="inlineStr">
+        <is>
+          <t>順序は Repository の返却順を保つ</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="34" customHeight="1">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>保存内容</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>INSERT INTO notifications (user_id, type, request_id, message, is_read) VALUES (?, ?, ?, ?, FALSE)。created_at / updated_at は DB の DEFAULT CURRENT_TIMESTAMP（DB セッションが JST であること。7.3 参照）</t>
-        </is>
-      </c>
-      <c r="C180" s="8" t="n"/>
-      <c r="D180" s="8" t="n"/>
-      <c r="E180" s="8" t="n"/>
-      <c r="F180" s="9" t="n"/>
-    </row>
-    <row r="181" ht="49" customHeight="1">
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>Repository が空リストを返す</t>
+        </is>
+      </c>
+      <c r="D180" s="9" t="n"/>
+      <c r="E180" s="4" t="inlineStr">
+        <is>
+          <t>notifications = []（null でない）</t>
+        </is>
+      </c>
+      <c r="F180" s="4" t="inlineStr"/>
+    </row>
+    <row r="181" ht="34" customHeight="1">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>type / requestId</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>type は NotificationType の7値（REQUEST_SUBMITTED / REQUEST_APPROVED / REQUEST_RETURNED / REQUEST_REJECTED / REQUEST_WITHDRAWN / LEAVE_GRANTED / LEAVE_ALERT）。requestId は REQUEST_* で必須、LEAVE_* は null。SCR-101『通知を選択 → 関連する申請へ遷移』は requestId があれば SCR-106 の該当申請へ遷移することで実現する（旧『SCR-106 で代替』の記述は廃止）</t>
-        </is>
-      </c>
-      <c r="C181" s="8" t="n"/>
-      <c r="D181" s="8" t="n"/>
-      <c r="E181" s="8" t="n"/>
-      <c r="F181" s="9" t="n"/>
-    </row>
-    <row r="182" ht="19" customHeight="1">
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>created_at = 2026-10-02T17:30:00 の通知</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="n"/>
+      <c r="E181" s="4" t="inlineStr">
+        <is>
+          <t>createdAt = "2026-10-02T17:30:00+09:00"</t>
+        </is>
+      </c>
+      <c r="F181" s="4" t="inlineStr">
+        <is>
+          <t>AppTime#toIso</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="49" customHeight="1">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>message の長さ</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>VARCHAR(500)。500 文字を超える場合は notify 内で切り詰める（DB 制約違反の防止）</t>
-        </is>
-      </c>
-      <c r="C182" s="8" t="n"/>
-      <c r="D182" s="8" t="n"/>
-      <c r="E182" s="8" t="n"/>
-      <c r="F182" s="9" t="n"/>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>呼び出しの引数</t>
+        </is>
+      </c>
+      <c r="D182" s="9" t="n"/>
+      <c r="E182" s="4" t="inlineStr">
+        <is>
+          <t>findTop50By…(userId) が JWT の userId で1回だけ呼ばれる</t>
+        </is>
+      </c>
+      <c r="F182" s="4" t="inlineStr">
+        <is>
+          <t>他人の userId は使えない</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="19" customHeight="1">
-      <c r="A183" s="4" t="inlineStr">
-        <is>
-          <t>トランザクション</t>
-        </is>
-      </c>
-      <c r="B183" s="4" t="inlineStr">
-        <is>
-          <t>呼び出し元の @Transactional に参加（REQUIRED）。通知の登録に失敗した場合は業務処理ごとロールバックされる</t>
-        </is>
-      </c>
+      <c r="A183" s="6" t="inlineStr">
+        <is>
+          <t>ONL-019: NotificationService#markAsRead（Mockito）</t>
+        </is>
+      </c>
+      <c r="B183" s="8" t="n"/>
       <c r="C183" s="8" t="n"/>
       <c r="D183" s="8" t="n"/>
       <c r="E183" s="8" t="n"/>
@@ -9158,796 +9288,352 @@
     <row r="184" ht="19" customHeight="1">
       <c r="A184" s="6" t="inlineStr">
         <is>
-          <t>ONL-019 existsMonthly の呼出し元（参照）</t>
-        </is>
-      </c>
-      <c r="B184" s="8" t="n"/>
-      <c r="C184" s="8" t="n"/>
-      <c r="D184" s="8" t="n"/>
-      <c r="E184" s="8" t="n"/>
-      <c r="F184" s="9" t="n"/>
-    </row>
-    <row r="185" ht="19" customHeight="1">
-      <c r="A185" s="6" t="inlineStr">
-        <is>
-          <t>呼出し元</t>
-        </is>
-      </c>
-      <c r="B185" s="6" t="inlineStr">
-        <is>
-          <t>用途</t>
-        </is>
-      </c>
-      <c r="C185" s="8" t="n"/>
-      <c r="D185" s="8" t="n"/>
-      <c r="E185" s="8" t="n"/>
-      <c r="F185" s="9" t="n"/>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B184" s="6" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C184" s="6" t="inlineStr">
+        <is>
+          <t>観点・条件</t>
+        </is>
+      </c>
+      <c r="D184" s="9" t="n"/>
+      <c r="E184" s="6" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="F184" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="49" customHeight="1">
+      <c r="A185" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B185" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>本人の未読通知</t>
+        </is>
+      </c>
+      <c r="D185" s="9" t="n"/>
+      <c r="E185" s="4" t="inlineStr">
+        <is>
+          <t>markAsRead(id, userId) が1回呼ばれ、応答の isRead = true</t>
+        </is>
+      </c>
+      <c r="F185" s="4" t="inlineStr"/>
     </row>
     <row r="186" ht="49" customHeight="1">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>BAT-002（年5日取得義務アラート）</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>宛先ごとに existsMonthly(宛先, LEAVE_ALERT, 先頭キー『[対象者ID:{id} 付与日:{yyyy-MM-dd}]』, 当月)（4 引数 overload）が false のときだけ notify する（同月・同一対象者・同一付与日で1回まで）。対象行の抽出は ONL-013 の LeaveBalanceService#findAlertBaseRows。3 引数版は対象者を区別できないため BAT-002 では使わない</t>
-        </is>
-      </c>
-      <c r="C186" s="8" t="n"/>
-      <c r="D186" s="8" t="n"/>
-      <c r="E186" s="8" t="n"/>
-      <c r="F186" s="9" t="n"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="7" t="inlineStr">
-        <is>
-          <t>⑥ 単体テスト観点（関連 ONL の tests を引用）</t>
-        </is>
-      </c>
-      <c r="B188" s="8" t="n"/>
-      <c r="C188" s="8" t="n"/>
-      <c r="D188" s="8" t="n"/>
-      <c r="E188" s="8" t="n"/>
-      <c r="F188" s="9" t="n"/>
-    </row>
-    <row r="189" ht="19" customHeight="1">
-      <c r="A189" s="6" t="inlineStr">
-        <is>
-          <t>ONL-005: NotificationService#notify（Mockito / @DataJpaTest）</t>
-        </is>
-      </c>
-      <c r="B189" s="8" t="n"/>
-      <c r="C189" s="8" t="n"/>
-      <c r="D189" s="8" t="n"/>
-      <c r="E189" s="8" t="n"/>
-      <c r="F189" s="9" t="n"/>
-    </row>
-    <row r="190" ht="19" customHeight="1">
-      <c r="A190" s="6" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B190" s="6" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="C190" s="6" t="inlineStr">
-        <is>
-          <t>観点・条件</t>
-        </is>
-      </c>
-      <c r="D190" s="9" t="n"/>
-      <c r="E190" s="6" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="F190" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="64" customHeight="1">
-      <c r="A191" s="4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B191" s="4" t="inlineStr">
-        <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="C191" s="4" t="inlineStr">
-        <is>
-          <t>type=REQUEST_SUBMITTED・requestId=15・message あり</t>
-        </is>
-      </c>
-      <c r="D191" s="9" t="n"/>
-      <c r="E191" s="4" t="inlineStr">
-        <is>
-          <t>Notification が save され、userId / type / requestId / message が入力どおり、read=false</t>
-        </is>
-      </c>
-      <c r="F191" s="4" t="inlineStr">
-        <is>
-          <t>INSERT 列は user_id, type, request_id, message, is_read</t>
-        </is>
-      </c>
-    </row>
-    <row r="192" ht="34" customHeight="1">
-      <c r="A192" s="4" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B192" s="4" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="C192" s="4" t="inlineStr">
-        <is>
-          <t>type=LEAVE_GRANTED・requestId=null</t>
-        </is>
-      </c>
-      <c r="D192" s="9" t="n"/>
-      <c r="E192" s="4" t="inlineStr">
-        <is>
-          <t>requestId=null で登録できる</t>
-        </is>
-      </c>
-      <c r="F192" s="4" t="inlineStr">
-        <is>
-          <t>LEAVE_* は申請に紐づかない</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="64" customHeight="1">
-      <c r="A193" s="4" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B193" s="4" t="inlineStr">
+      <c r="C186" s="4" t="inlineStr">
+        <is>
+          <t>本人の既読通知</t>
+        </is>
+      </c>
+      <c r="D186" s="9" t="n"/>
+      <c r="E186" s="4" t="inlineStr">
+        <is>
+          <t>markAsRead（UPDATE）は呼ばれず、応答は isRead = true で正常終了</t>
+        </is>
+      </c>
+      <c r="F186" s="4" t="inlineStr">
+        <is>
+          <t>冪等</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="34" customHeight="1">
+      <c r="A187" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B187" s="4" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr">
+        <is>
+          <t>findByIdAndUserId が empty（存在しない ID）</t>
+        </is>
+      </c>
+      <c r="D187" s="9" t="n"/>
+      <c r="E187" s="4" t="inlineStr">
+        <is>
+          <t>BusinessException E-010 / 403</t>
+        </is>
+      </c>
+      <c r="F187" s="4" t="inlineStr">
+        <is>
+          <t>UPDATE は呼ばれない</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="49" customHeight="1">
+      <c r="A188" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C188" s="4" t="inlineStr">
+        <is>
+          <t>他人の通知 ID（Repository は empty を返す）</t>
+        </is>
+      </c>
+      <c r="D188" s="9" t="n"/>
+      <c r="E188" s="4" t="inlineStr">
+        <is>
+          <t>BusinessException E-010 / 403。存在しない場合と同じメッセージ</t>
+        </is>
+      </c>
+      <c r="F188" s="4" t="inlineStr">
+        <is>
+          <t>区別しないことの確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="34" customHeight="1">
+      <c r="A189" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B189" s="4" t="inlineStr">
         <is>
           <t>境界</t>
         </is>
       </c>
-      <c r="C193" s="4" t="inlineStr">
-        <is>
-          <t>message が500文字／501文字（サロゲートペアを含む場合も）</t>
-        </is>
-      </c>
-      <c r="D193" s="9" t="n"/>
-      <c r="E193" s="4" t="inlineStr">
-        <is>
-          <t>500文字はそのまま。501文字は500文字（末尾「…」）に切り詰め、DB 制約違反にならない</t>
-        </is>
-      </c>
-      <c r="F193" s="4" t="inlineStr">
-        <is>
-          <t>コードポイント単位</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="34" customHeight="1">
-      <c r="A194" s="4" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B194" s="4" t="inlineStr">
-        <is>
-          <t>異常</t>
-        </is>
-      </c>
-      <c r="C194" s="4" t="inlineStr">
-        <is>
-          <t>userId = null／type = null／未知の type／message が空白のみ</t>
-        </is>
-      </c>
-      <c r="D194" s="9" t="n"/>
-      <c r="E194" s="4" t="inlineStr">
-        <is>
-          <t>IllegalArgumentException。save は呼ばれない</t>
-        </is>
-      </c>
-      <c r="F194" s="4" t="inlineStr">
-        <is>
-          <t>呼出し側のバグ（API では E-012）</t>
-        </is>
-      </c>
-    </row>
-    <row r="195" ht="34" customHeight="1">
-      <c r="A195" s="4" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B195" s="4" t="inlineStr">
-        <is>
-          <t>異常</t>
-        </is>
-      </c>
-      <c r="C195" s="4" t="inlineStr">
-        <is>
-          <t>type=REQUEST_APPROVED で requestId = null</t>
-        </is>
-      </c>
-      <c r="D195" s="9" t="n"/>
-      <c r="E195" s="4" t="inlineStr">
-        <is>
-          <t>IllegalArgumentException</t>
-        </is>
-      </c>
-      <c r="F195" s="4" t="inlineStr">
-        <is>
-          <t>REQUEST_BOUND は requestId 必須</t>
-        </is>
-      </c>
-    </row>
-    <row r="196" ht="49" customHeight="1">
-      <c r="A196" s="4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B196" s="4" t="inlineStr">
-        <is>
-          <t>異常</t>
-        </is>
-      </c>
-      <c r="C196" s="4" t="inlineStr">
-        <is>
-          <t>存在しない requestId（@DataJpaTest）</t>
-        </is>
-      </c>
-      <c r="D196" s="9" t="n"/>
-      <c r="E196" s="4" t="inlineStr">
-        <is>
-          <t>DataIntegrityViolationException（fk_notifications_request_id）</t>
-        </is>
-      </c>
-      <c r="F196" s="4" t="inlineStr">
-        <is>
-          <t>requests の INSERT 後に呼ぶ前提の確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="197" ht="19" customHeight="1">
-      <c r="A197" s="6" t="inlineStr">
-        <is>
-          <t>ONL-019: NotificationService#getNotifications（Mockito）</t>
-        </is>
-      </c>
-      <c r="B197" s="8" t="n"/>
-      <c r="C197" s="8" t="n"/>
-      <c r="D197" s="8" t="n"/>
-      <c r="E197" s="8" t="n"/>
-      <c r="F197" s="9" t="n"/>
-    </row>
-    <row r="198" ht="19" customHeight="1">
-      <c r="A198" s="6" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B198" s="6" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="C198" s="6" t="inlineStr">
-        <is>
-          <t>観点・条件</t>
-        </is>
-      </c>
-      <c r="D198" s="9" t="n"/>
-      <c r="E198" s="6" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="F198" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="199" ht="49" customHeight="1">
-      <c r="A199" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B199" s="4" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="C199" s="4" t="inlineStr">
-        <is>
-          <t>Repository が3件（新しい順）を返す</t>
-        </is>
-      </c>
-      <c r="D199" s="9" t="n"/>
-      <c r="E199" s="4" t="inlineStr">
-        <is>
-          <t>notifications が同じ順で3件。isRead が Entity の値どおり</t>
-        </is>
-      </c>
-      <c r="F199" s="4" t="inlineStr">
-        <is>
-          <t>順序は Repository の返却順を保つ</t>
-        </is>
-      </c>
-    </row>
-    <row r="200" ht="34" customHeight="1">
-      <c r="A200" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B200" s="4" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="C200" s="4" t="inlineStr">
-        <is>
-          <t>Repository が空リストを返す</t>
-        </is>
-      </c>
-      <c r="D200" s="9" t="n"/>
-      <c r="E200" s="4" t="inlineStr">
-        <is>
-          <t>notifications = []（null でない）</t>
-        </is>
-      </c>
-      <c r="F200" s="4" t="inlineStr"/>
-    </row>
-    <row r="201" ht="34" customHeight="1">
-      <c r="A201" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B201" s="4" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="C201" s="4" t="inlineStr">
-        <is>
-          <t>created_at = 2026-10-02T17:30:00 の通知</t>
-        </is>
-      </c>
-      <c r="D201" s="9" t="n"/>
-      <c r="E201" s="4" t="inlineStr">
-        <is>
-          <t>createdAt = "2026-10-02T17:30:00+09:00"</t>
-        </is>
-      </c>
-      <c r="F201" s="4" t="inlineStr">
-        <is>
-          <t>AppTime#toIso</t>
-        </is>
-      </c>
-    </row>
-    <row r="202" ht="49" customHeight="1">
-      <c r="A202" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B202" s="4" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="C202" s="4" t="inlineStr">
-        <is>
-          <t>呼び出しの引数</t>
-        </is>
-      </c>
-      <c r="D202" s="9" t="n"/>
-      <c r="E202" s="4" t="inlineStr">
-        <is>
-          <t>findTop50By…(userId) が JWT の userId で1回だけ呼ばれる</t>
-        </is>
-      </c>
-      <c r="F202" s="4" t="inlineStr">
-        <is>
-          <t>他人の userId は使えない</t>
-        </is>
-      </c>
-    </row>
-    <row r="203" ht="19" customHeight="1">
-      <c r="A203" s="6" t="inlineStr">
-        <is>
-          <t>ONL-019: NotificationService#markAsRead（Mockito）</t>
-        </is>
-      </c>
-      <c r="B203" s="8" t="n"/>
-      <c r="C203" s="8" t="n"/>
-      <c r="D203" s="8" t="n"/>
-      <c r="E203" s="8" t="n"/>
-      <c r="F203" s="9" t="n"/>
-    </row>
-    <row r="204" ht="19" customHeight="1">
-      <c r="A204" s="6" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B204" s="6" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="C204" s="6" t="inlineStr">
-        <is>
-          <t>観点・条件</t>
-        </is>
-      </c>
-      <c r="D204" s="9" t="n"/>
-      <c r="E204" s="6" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="F204" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="205" ht="49" customHeight="1">
-      <c r="A205" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B205" s="4" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="C205" s="4" t="inlineStr">
-        <is>
-          <t>本人の未読通知</t>
-        </is>
-      </c>
-      <c r="D205" s="9" t="n"/>
-      <c r="E205" s="4" t="inlineStr">
-        <is>
-          <t>markAsRead(id, userId) が1回呼ばれ、応答の isRead = true</t>
-        </is>
-      </c>
-      <c r="F205" s="4" t="inlineStr"/>
-    </row>
-    <row r="206" ht="49" customHeight="1">
-      <c r="A206" s="4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B206" s="4" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="C206" s="4" t="inlineStr">
-        <is>
-          <t>本人の既読通知</t>
-        </is>
-      </c>
-      <c r="D206" s="9" t="n"/>
-      <c r="E206" s="4" t="inlineStr">
-        <is>
-          <t>markAsRead（UPDATE）は呼ばれず、応答は isRead = true で正常終了</t>
-        </is>
-      </c>
-      <c r="F206" s="4" t="inlineStr">
-        <is>
-          <t>冪等</t>
-        </is>
-      </c>
-    </row>
-    <row r="207" ht="34" customHeight="1">
-      <c r="A207" s="4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B207" s="4" t="inlineStr">
-        <is>
-          <t>異常</t>
-        </is>
-      </c>
-      <c r="C207" s="4" t="inlineStr">
-        <is>
-          <t>findByIdAndUserId が empty（存在しない ID）</t>
-        </is>
-      </c>
-      <c r="D207" s="9" t="n"/>
-      <c r="E207" s="4" t="inlineStr">
-        <is>
-          <t>BusinessException E-010 / 403</t>
-        </is>
-      </c>
-      <c r="F207" s="4" t="inlineStr">
-        <is>
-          <t>UPDATE は呼ばれない</t>
-        </is>
-      </c>
-    </row>
-    <row r="208" ht="49" customHeight="1">
-      <c r="A208" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B208" s="4" t="inlineStr">
-        <is>
-          <t>異常</t>
-        </is>
-      </c>
-      <c r="C208" s="4" t="inlineStr">
-        <is>
-          <t>他人の通知 ID（Repository は empty を返す）</t>
-        </is>
-      </c>
-      <c r="D208" s="9" t="n"/>
-      <c r="E208" s="4" t="inlineStr">
-        <is>
-          <t>BusinessException E-010 / 403。存在しない場合と同じメッセージ</t>
-        </is>
-      </c>
-      <c r="F208" s="4" t="inlineStr">
-        <is>
-          <t>区別しないことの確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="209" ht="34" customHeight="1">
-      <c r="A209" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B209" s="4" t="inlineStr">
-        <is>
-          <t>境界</t>
-        </is>
-      </c>
-      <c r="C209" s="4" t="inlineStr">
+      <c r="C189" s="4" t="inlineStr">
         <is>
           <t>UPDATE の戻り値が 0（同時に別リクエストが既読化済み）</t>
         </is>
       </c>
-      <c r="D209" s="9" t="n"/>
-      <c r="E209" s="4" t="inlineStr">
+      <c r="D189" s="9" t="n"/>
+      <c r="E189" s="4" t="inlineStr">
         <is>
           <t>例外にならず 200 相当で応答する</t>
         </is>
       </c>
-      <c r="F209" s="4" t="inlineStr">
+      <c r="F189" s="4" t="inlineStr">
         <is>
           <t>同時実行</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="204">
-    <mergeCell ref="B106:F106"/>
+  <mergeCells count="184">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B129:F129"/>
+    <mergeCell ref="C150:F150"/>
+    <mergeCell ref="A183:F183"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B81:F81"/>
-    <mergeCell ref="C144:F144"/>
-    <mergeCell ref="C191:D191"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="A189:F189"/>
+    <mergeCell ref="C122:F122"/>
+    <mergeCell ref="C153:F153"/>
     <mergeCell ref="C72:F72"/>
-    <mergeCell ref="B122:F122"/>
+    <mergeCell ref="C172:D172"/>
     <mergeCell ref="B71:F71"/>
-    <mergeCell ref="C125:F125"/>
+    <mergeCell ref="C187:D187"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="B131:F131"/>
-    <mergeCell ref="A86:F86"/>
     <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="C184:D184"/>
     <mergeCell ref="B52:F52"/>
-    <mergeCell ref="B180:F180"/>
-    <mergeCell ref="A160:F160"/>
+    <mergeCell ref="C171:D171"/>
+    <mergeCell ref="A47:F47"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B60:F60"/>
-    <mergeCell ref="A159:F159"/>
+    <mergeCell ref="C173:D173"/>
     <mergeCell ref="A20:F20"/>
-    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="C107:F107"/>
     <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="A134:F134"/>
     <mergeCell ref="B166:F166"/>
-    <mergeCell ref="C172:F172"/>
     <mergeCell ref="C73:F73"/>
-    <mergeCell ref="B116:F116"/>
     <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C171:F171"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="C54:F54"/>
     <mergeCell ref="B108:F108"/>
     <mergeCell ref="E36:F36"/>
     <mergeCell ref="A40:F40"/>
-    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="C121:F121"/>
     <mergeCell ref="B84:F84"/>
-    <mergeCell ref="C93:F93"/>
+    <mergeCell ref="B143:F143"/>
     <mergeCell ref="B118:F118"/>
-    <mergeCell ref="C173:F173"/>
+    <mergeCell ref="B92:F92"/>
+    <mergeCell ref="B158:F158"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="C56:F56"/>
-    <mergeCell ref="B133:F133"/>
     <mergeCell ref="B15:F15"/>
-    <mergeCell ref="C190:D190"/>
+    <mergeCell ref="C105:F105"/>
+    <mergeCell ref="B142:F142"/>
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B94:F94"/>
+    <mergeCell ref="B160:F160"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B135:F135"/>
+    <mergeCell ref="B144:F144"/>
     <mergeCell ref="C30:D30"/>
-    <mergeCell ref="B185:F185"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B121:F121"/>
+    <mergeCell ref="C175:D175"/>
+    <mergeCell ref="B125:F125"/>
+    <mergeCell ref="C149:F149"/>
+    <mergeCell ref="C185:D185"/>
     <mergeCell ref="B96:F96"/>
-    <mergeCell ref="B167:F167"/>
     <mergeCell ref="B70:F70"/>
-    <mergeCell ref="C111:F111"/>
     <mergeCell ref="A33:F33"/>
-    <mergeCell ref="C200:D200"/>
-    <mergeCell ref="A188:F188"/>
-    <mergeCell ref="C92:F92"/>
+    <mergeCell ref="A85:F85"/>
+    <mergeCell ref="B111:F111"/>
+    <mergeCell ref="B120:F120"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="C175:F175"/>
-    <mergeCell ref="C202:D202"/>
-    <mergeCell ref="B107:F107"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B88:F88"/>
-    <mergeCell ref="B148:F148"/>
     <mergeCell ref="B82:F82"/>
-    <mergeCell ref="C192:D192"/>
     <mergeCell ref="B162:F162"/>
-    <mergeCell ref="C201:D201"/>
+    <mergeCell ref="C188:D188"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="B146:F146"/>
-    <mergeCell ref="C194:D194"/>
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="A48:F48"/>
-    <mergeCell ref="A176:F176"/>
+    <mergeCell ref="C181:D181"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="B68:F68"/>
     <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="C124:F124"/>
+    <mergeCell ref="A169:F169"/>
+    <mergeCell ref="C174:D174"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="C90:F90"/>
+    <mergeCell ref="C189:D189"/>
+    <mergeCell ref="C123:F123"/>
     <mergeCell ref="C76:F76"/>
     <mergeCell ref="B4:F4"/>
-    <mergeCell ref="C110:F110"/>
+    <mergeCell ref="B126:F126"/>
+    <mergeCell ref="C179:D179"/>
     <mergeCell ref="B109:F109"/>
+    <mergeCell ref="A177:F177"/>
     <mergeCell ref="B62:F62"/>
     <mergeCell ref="C91:F91"/>
+    <mergeCell ref="B141:F141"/>
+    <mergeCell ref="A164:F164"/>
     <mergeCell ref="B59:F59"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="A136:F136"/>
-    <mergeCell ref="A105:F105"/>
-    <mergeCell ref="C174:F174"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="A139:F139"/>
     <mergeCell ref="C57:F57"/>
-    <mergeCell ref="A154:F154"/>
+    <mergeCell ref="C155:F155"/>
     <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="C53:F53"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="B161:F161"/>
-    <mergeCell ref="C205:D205"/>
-    <mergeCell ref="A203:F203"/>
+    <mergeCell ref="A116:F116"/>
     <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B136:F136"/>
     <mergeCell ref="B145:F145"/>
     <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C193:D193"/>
+    <mergeCell ref="C151:F151"/>
+    <mergeCell ref="A100:F100"/>
     <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C58:F58"/>
-    <mergeCell ref="B181:F181"/>
+    <mergeCell ref="A140:F140"/>
+    <mergeCell ref="C176:D176"/>
     <mergeCell ref="B13:F13"/>
-    <mergeCell ref="C141:F141"/>
     <mergeCell ref="B44:C44"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="B87:F87"/>
     <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B178:F178"/>
+    <mergeCell ref="C178:D178"/>
     <mergeCell ref="B128:F128"/>
-    <mergeCell ref="C143:F143"/>
     <mergeCell ref="A34:F34"/>
-    <mergeCell ref="C94:F94"/>
     <mergeCell ref="B137:F137"/>
+    <mergeCell ref="C152:F152"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="A39:F39"/>
-    <mergeCell ref="B183:F183"/>
     <mergeCell ref="B65:F65"/>
-    <mergeCell ref="C127:F127"/>
-    <mergeCell ref="A49:F49"/>
-    <mergeCell ref="C142:F142"/>
-    <mergeCell ref="C209:D209"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="B139:F139"/>
     <mergeCell ref="B45:C45"/>
+    <mergeCell ref="C170:D170"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="A168:F168"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="C95:F95"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B110:F110"/>
     <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B47:C47"/>
     <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C195:D195"/>
-    <mergeCell ref="B100:F100"/>
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="C204:D204"/>
+    <mergeCell ref="C106:F106"/>
     <mergeCell ref="B165:F165"/>
     <mergeCell ref="B46:C46"/>
     <mergeCell ref="B66:F66"/>
-    <mergeCell ref="A120:F120"/>
-    <mergeCell ref="B140:F140"/>
     <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B155:F155"/>
-    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B93:F93"/>
     <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C170:F170"/>
     <mergeCell ref="B102:F102"/>
     <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C206:D206"/>
     <mergeCell ref="E35:F35"/>
     <mergeCell ref="B130:F130"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B77:F77"/>
+    <mergeCell ref="C154:F154"/>
+    <mergeCell ref="B86:F86"/>
     <mergeCell ref="B117:F117"/>
     <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C196:D196"/>
-    <mergeCell ref="B151:F151"/>
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B101:F101"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B132:F132"/>
-    <mergeCell ref="A184:F184"/>
+    <mergeCell ref="C180:D180"/>
     <mergeCell ref="B119:F119"/>
-    <mergeCell ref="C198:D198"/>
+    <mergeCell ref="A156:F156"/>
     <mergeCell ref="C74:F74"/>
-    <mergeCell ref="C126:F126"/>
     <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B103:F103"/>
     <mergeCell ref="B78:F78"/>
-    <mergeCell ref="C207:D207"/>
+    <mergeCell ref="C182:D182"/>
     <mergeCell ref="B112:F112"/>
     <mergeCell ref="A67:F67"/>
+    <mergeCell ref="B127:F127"/>
     <mergeCell ref="C55:F55"/>
+    <mergeCell ref="A148:F148"/>
+    <mergeCell ref="B49:F49"/>
     <mergeCell ref="C75:F75"/>
     <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="C199:D199"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B89:F89"/>
     <mergeCell ref="B104:F104"/>
-    <mergeCell ref="A197:F197"/>
     <mergeCell ref="B51:F51"/>
-    <mergeCell ref="C208:D208"/>
+    <mergeCell ref="C186:D186"/>
     <mergeCell ref="B79:F79"/>
-    <mergeCell ref="C169:F169"/>
     <mergeCell ref="B97:F97"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9961,7 +9647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F136"/>
+  <dimension ref="A1:F137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10207,7 +9893,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>NotificationService</t>
         </is>
       </c>
       <c r="C17" s="8" t="n"/>
@@ -10467,49 +10153,49 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="49" customHeight="1">
+    <row r="33" ht="79" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>1. findTop50ByUserIdOrderByCreatedAtDescIdDesc</t>
+          <t>1. existsByUserIdAndTypeAndMessageStartingWithAndCreatedAtGreaterThanEqualAndCreatedAtLessThan</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>List&lt;Notification&gt; findTop50ByUserIdOrderByCreatedAtDescIdDesc(Long userId)</t>
+          <t>boolean existsByUserIdAndTypeAndMessageStartingWithAndCreatedAtGreaterThanEqualAndCreatedAtLessThan( Long userId, String type, String messagePrefix, LocalDateTime from, LocalDateTime to)</t>
         </is>
       </c>
       <c r="C33" s="9" t="n"/>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>List&lt;Notification&gt;</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>ONL-019</t>
+          <t>BAT-002, ONL-019</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Repository（Spring Data JPA・本処理で追加）</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="34" customHeight="1">
+          <t>Service ＋ Repository（本書で ONL-019 に追加）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="49" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2. findByIdAndUserId</t>
+          <t>2. findTop50ByUserIdOrderByCreatedAtDescIdDesc</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>Optional&lt;Notification&gt; findByIdAndUserId(Long id, Long userId)</t>
+          <t>List&lt;Notification&gt; findTop50ByUserIdOrderByCreatedAtDescIdDesc(Long userId)</t>
         </is>
       </c>
       <c r="C34" s="9" t="n"/>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Optional&lt;Notification&gt;</t>
+          <t>List&lt;Notification&gt;</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -10523,21 +10209,21 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="64" customHeight="1">
+    <row r="35" ht="34" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>3. existsByUserIdAndTypeAndCreatedAtGreaterThanEqualAndCreatedAtLessThan</t>
+          <t>3. findByIdAndUserId</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>boolean existsByUserIdAndTypeAndCreatedAtGreaterThanEqualAndCreatedAtLessThan(Long userId, String type, LocalDateTime from, LocalDateTime to)</t>
+          <t>Optional&lt;Notification&gt; findByIdAndUserId(Long id, Long userId)</t>
         </is>
       </c>
       <c r="C35" s="9" t="n"/>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>Optional&lt;Notification&gt;</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -10551,15 +10237,15 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="79" customHeight="1">
+    <row r="36" ht="64" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>4. existsByUserIdAndTypeAndMessageStartingWithAndCreatedAtGreaterThanEqualAndCreatedAtLessThan</t>
+          <t>4. existsByUserIdAndTypeAndCreatedAtGreaterThanEqualAndCreatedAtLessThan</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>boolean existsByUserIdAndTypeAndMessageStartingWithAndCreatedAtGreaterThanEqualAndCreatedAtLessThan( Long userId, String type, String messagePrefix, LocalDateTime from, LocalDateTime to)</t>
+          <t>boolean existsByUserIdAndTypeAndCreatedAtGreaterThanEqualAndCreatedAtLessThan(Long userId, String type, LocalDateTime from, LocalDateTime to)</t>
         </is>
       </c>
       <c r="C36" s="9" t="n"/>
@@ -10622,7 +10308,7 @@
     <row r="39" ht="19" customHeight="1">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>③-2-1  NotificationRepository#findTop50ByUserIdOrderByCreatedAtDescIdDesc  （一覧 No. 1）</t>
+          <t>③-2-1  NotificationRepository#existsByUserIdAndTypeAndMessageStartingWithAndCreatedAtGreaterThanEqualAndCreatedAtLessThan  （一覧 No. 1）</t>
         </is>
       </c>
       <c r="B39" s="8" t="n"/>
@@ -10639,7 +10325,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Repository（Spring Data JPA・本処理で追加）</t>
+          <t>Service ＋ Repository（本書で ONL-019 に追加）</t>
         </is>
       </c>
       <c r="C40" s="8" t="n"/>
@@ -10647,7 +10333,7 @@
       <c r="E40" s="8" t="n"/>
       <c r="F40" s="9" t="n"/>
     </row>
-    <row r="41" ht="19" customHeight="1">
+    <row r="41" ht="34" customHeight="1">
       <c r="A41" s="10" t="inlineStr">
         <is>
           <t>シグネチャ</t>
@@ -10655,7 +10341,7 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>List&lt;Notification&gt; findTop50ByUserIdOrderByCreatedAtDescIdDesc(Long userId)</t>
+          <t>boolean existsByUserIdAndTypeAndMessageStartingWithAndCreatedAtGreaterThanEqualAndCreatedAtLessThan( Long userId, String type, String messagePrefix, LocalDateTime from, LocalDateTime to)</t>
         </is>
       </c>
       <c r="C41" s="8" t="n"/>
@@ -10663,7 +10349,7 @@
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="9" t="n"/>
     </row>
-    <row r="42" ht="19" customHeight="1">
+    <row r="42" ht="34" customHeight="1">
       <c r="A42" s="10" t="inlineStr">
         <is>
           <t>説明</t>
@@ -10671,7 +10357,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>ユーザーの通知を、作成日時の新しい順（同時刻は ID の大きい順）で最大50件返す。</t>
+          <t>指定ユーザー・指定種別の通知のうち、本文が keyPrefix で始まるもの（対象者・付与日が同じもの）が、指定した年月（JST）に既に作成されているかを返す。</t>
         </is>
       </c>
       <c r="C42" s="8" t="n"/>
@@ -10687,7 +10373,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>interface NotificationRepository extends JpaRepository&lt;Notification, Long&gt;</t>
+          <t>@Transactional(readOnly = true)（Service）</t>
         </is>
       </c>
       <c r="C43" s="8" t="n"/>
@@ -10728,7 +10414,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>通知の宛先ユーザーID</t>
+          <t>宛先</t>
         </is>
       </c>
       <c r="D45" s="8" t="n"/>
@@ -10736,64 +10422,74 @@
       <c r="F45" s="9" t="n"/>
     </row>
     <row r="46" ht="19" customHeight="1">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <t>戻り値</t>
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>type</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>List&lt;Notification&gt;（該当なしは空リスト）</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="n"/>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>通知種別（BAT-002 は NotificationType.LEAVE_ALERT）</t>
+        </is>
+      </c>
       <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="9" t="n"/>
     </row>
     <row r="47" ht="19" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>例外</t>
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>keyPrefix</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="n"/>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>本文の先頭キー（MandatoryLeaveMessages.key の戻り値。ワイルドカード不要）</t>
+        </is>
+      </c>
       <c r="D47" s="8" t="n"/>
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="9" t="n"/>
     </row>
     <row r="48" ht="19" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>トランザクション</t>
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>yearMonth</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>呼出し元 Service のトランザクションに参加（読取は Spring Data 既定の readOnly）</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="n"/>
+          <t>YearMonth</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>確認する年月（JST の暦月）</t>
+        </is>
+      </c>
       <c r="D48" s="8" t="n"/>
       <c r="E48" s="8" t="n"/>
       <c r="F48" s="9" t="n"/>
     </row>
-    <row r="49" ht="49" customHeight="1">
+    <row r="49" ht="19" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>処理詳細（疑似コード）</t>
-        </is>
-      </c>
-      <c r="B49" s="15" t="inlineStr">
-        <is>
-          <t>実装クラスは作らない。メソッド名（Top50 / OrderBy…Desc）から次の SQL が生成される。
-SELECT * FROM notifications WHERE user_id = ? ORDER BY created_at DESC, id DESC LIMIT 50
-（PostgreSQL では FETCH FIRST 50 ROWS ONLY / LIMIT 形式）</t>
+          <t>戻り値</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>boolean</t>
         </is>
       </c>
       <c r="C49" s="8" t="n"/>
@@ -10804,12 +10500,12 @@
     <row r="50" ht="19" customHeight="1">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>呼出先</t>
+          <t>例外</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>（DB: notifications）</t>
+          <t>DataAccessException</t>
         </is>
       </c>
       <c r="C50" s="8" t="n"/>
@@ -10820,12 +10516,12 @@
     <row r="51" ht="19" customHeight="1">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>呼出元</t>
+          <t>トランザクション</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>NotificationService#getNotifications（ONL-019）</t>
+          <t>@Transactional(readOnly = true)（Service）</t>
         </is>
       </c>
       <c r="C51" s="8" t="n"/>
@@ -10833,15 +10529,26 @@
       <c r="E51" s="8" t="n"/>
       <c r="F51" s="9" t="n"/>
     </row>
-    <row r="52" ht="19" customHeight="1">
+    <row r="52" ht="184" customHeight="1">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>関連 ONL</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>ONL-019 通知一覧取得（API-019）</t>
+          <t>処理詳細（疑似コード）</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>public boolean existsMonthly(Long userId, String type, String keyPrefix, YearMonth yearMonth) {
+    LocalDateTime from = yearMonth.atDay(1).atStartOfDay();                    // 当月 1 日 00:00:00（JST）
+    LocalDateTime to   = yearMonth.plusMonths(1).atDay(1).atStartOfDay();      // 翌月 1 日 00:00:00（含まない）
+    return notificationRepository
+        .existsByUserIdAndTypeAndMessageStartingWithAndCreatedAtGreaterThanEqualAndCreatedAtLessThan(
+            userId, type, keyPrefix, from, to);
+}
+-- 実行される SQL（StartingWith は param || '%' に変換され、% _ \ はエスケープされる）
+SELECT 1 FROM notifications
+ WHERE user_id = ? AND type = ? AND message LIKE ? ESCAPE '\'
+   AND created_at &gt;= ? AND created_at &lt; ?
+ LIMIT 1</t>
         </is>
       </c>
       <c r="C52" s="8" t="n"/>
@@ -10849,16 +10556,15 @@
       <c r="E52" s="8" t="n"/>
       <c r="F52" s="9" t="n"/>
     </row>
-    <row r="53" ht="49" customHeight="1">
+    <row r="53" ht="19" customHeight="1">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>呼出先</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>idx_notif_user (user_id, is_read) で user_id による絞り込みが効く。並び替えは絞り込み後の行（本人分のみ、年間数十件）で行うため性能上問題ない。
-id を第2ソートキーにして、created_at が同一でも順序を決定的にする。</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C53" s="8" t="n"/>
@@ -10867,12 +10573,16 @@
       <c r="F53" s="9" t="n"/>
     </row>
     <row r="54" ht="19" customHeight="1">
-      <c r="A54" s="14" t="inlineStr">
-        <is>
-          <t>③-2-2  NotificationRepository#findByIdAndUserId  （一覧 No. 2）</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="n"/>
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>呼出元</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>NotificationService#existsMonthly（ONL-019）</t>
+        </is>
+      </c>
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="8" t="n"/>
       <c r="E54" s="8" t="n"/>
@@ -10881,12 +10591,12 @@
     <row r="55" ht="19" customHeight="1">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>種別</t>
+          <t>関連 ONL</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Repository（Spring Data JPA・本処理で追加）</t>
+          <t>BAT-002 年5日取得義務アラート（バッチ）、ONL-019 通知一覧取得（API-019）</t>
         </is>
       </c>
       <c r="C55" s="8" t="n"/>
@@ -10894,15 +10604,18 @@
       <c r="E55" s="8" t="n"/>
       <c r="F55" s="9" t="n"/>
     </row>
-    <row r="56" ht="19" customHeight="1">
+    <row r="56" ht="124" customHeight="1">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>シグネチャ</t>
-        </is>
-      </c>
-      <c r="B56" s="15" t="inlineStr">
-        <is>
-          <t>Optional&lt;Notification&gt; findByIdAndUserId(Long id, Long userId)</t>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>【ONL-019 との関係】ONL-019 の existsMonthly(Long userId, String type, YearMonth yearMonth) は『宛先・type・月』だけで判定し、対象者・付与日を区別できない。管理者は同じ月に複数の対象者分を受け取るため、3 引数版を使うと 2 人目以降が『送信済み』と誤判定されて通知されない。そのため BAT-002 は keyPrefix を加えた本 overload を使う。ONL-019 への追記が必要（最終報告に記載）。3 引数版は本書では使用しない。
+同時に走った場合の厳密な排他は無い（D-6）。
+idx_notif_user (user_id, is_read) が user_id で効く。1 ユーザーの通知は多くて年数百件のため type・前方一致・月範囲の絞り込みで問題ない。
+created_at は DB の DEFAULT CURRENT_TIMESTAMP。DB セッションの JST は hikari connection-init-sql で設定済み（7.3）のため、JST の暦月で判定できる。</t>
         </is>
       </c>
       <c r="C56" s="8" t="n"/>
@@ -10910,15 +10623,20 @@
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="9" t="n"/>
     </row>
-    <row r="57" ht="19" customHeight="1">
+    <row r="57" ht="94" customHeight="1">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>説明</t>
+          <t>他 ONL の記述
+（ONL-019）</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>通知ID とユーザーIDの両方が一致する通知を1件返す（所有確認を兼ねる）。</t>
+          <t>説明: 指定ユーザー・種別で本文が messagePrefix で始まる通知が期間 [from, to) に存在するかを返す。
+例外: なし
+処理詳細（差分あり）:
+SELECT 1 FROM notifications WHERE user_id = ? AND type = ? AND message LIKE ? ESCAPE '\' AND created_at &gt;= ? AND created_at &lt; ? LIMIT 1   -- 実際は Hibernate が発行（% _ \ はエスケープ）
+備考: 3 引数版用の existsByUserIdAndTypeAndCreatedAtGreaterThanEqualAndCreatedAtLessThan とは別メソッド。</t>
         </is>
       </c>
       <c r="C57" s="8" t="n"/>
@@ -10927,77 +10645,61 @@
       <c r="F57" s="9" t="n"/>
     </row>
     <row r="58" ht="19" customHeight="1">
-      <c r="A58" s="10" t="inlineStr">
-        <is>
-          <t>アノテーション</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>同上</t>
-        </is>
-      </c>
+      <c r="A58" s="14" t="inlineStr">
+        <is>
+          <t>③-2-2  NotificationRepository#findTop50ByUserIdOrderByCreatedAtDescIdDesc  （一覧 No. 2）</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="n"/>
       <c r="C58" s="8" t="n"/>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
       <c r="F58" s="9" t="n"/>
     </row>
     <row r="59" ht="19" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>引数名</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Repository（Spring Data JPA・本処理で追加）</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="n"/>
       <c r="D59" s="8" t="n"/>
       <c r="E59" s="8" t="n"/>
       <c r="F59" s="9" t="n"/>
     </row>
     <row r="60" ht="19" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>通知ID</t>
-        </is>
-      </c>
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>シグネチャ</t>
+        </is>
+      </c>
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t>List&lt;Notification&gt; findTop50ByUserIdOrderByCreatedAtDescIdDesc(Long userId)</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
       <c r="F60" s="9" t="n"/>
     </row>
     <row r="61" ht="19" customHeight="1">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>userId</t>
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>ログインユーザーID</t>
-        </is>
-      </c>
+          <t>ユーザーの通知を、作成日時の新しい順（同時刻は ID の大きい順）で最大50件返す。</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="n"/>
       <c r="D61" s="8" t="n"/>
       <c r="E61" s="8" t="n"/>
       <c r="F61" s="9" t="n"/>
@@ -11005,12 +10707,12 @@
     <row r="62" ht="19" customHeight="1">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>戻り値</t>
+          <t>アノテーション</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Optional&lt;Notification&gt;（存在しない／他人の通知は Optional.empty()）</t>
+          <t>interface NotificationRepository extends JpaRepository&lt;Notification, Long&gt;</t>
         </is>
       </c>
       <c r="C62" s="8" t="n"/>
@@ -11019,46 +10721,54 @@
       <c r="F62" s="9" t="n"/>
     </row>
     <row r="63" ht="19" customHeight="1">
-      <c r="A63" s="10" t="inlineStr">
-        <is>
-          <t>例外</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="C63" s="8" t="n"/>
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>引数名</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="9" t="n"/>
     </row>
     <row r="64" ht="19" customHeight="1">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t>トランザクション</t>
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>userId</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>呼出し元 Service のトランザクションに参加（読取は Spring Data 既定の readOnly）</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="n"/>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>通知の宛先ユーザーID</t>
+        </is>
+      </c>
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
       <c r="F64" s="9" t="n"/>
     </row>
-    <row r="65" ht="34" customHeight="1">
+    <row r="65" ht="19" customHeight="1">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>処理詳細（疑似コード）</t>
-        </is>
-      </c>
-      <c r="B65" s="15" t="inlineStr">
-        <is>
-          <t>SELECT * FROM notifications WHERE id = ? AND user_id = ?</t>
+          <t>戻り値</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>List&lt;Notification&gt;（該当なしは空リスト）</t>
         </is>
       </c>
       <c r="C65" s="8" t="n"/>
@@ -11069,12 +10779,12 @@
     <row r="66" ht="19" customHeight="1">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>呼出先</t>
+          <t>例外</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>（DB: notifications）</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="C66" s="8" t="n"/>
@@ -11085,12 +10795,12 @@
     <row r="67" ht="19" customHeight="1">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>呼出元</t>
+          <t>トランザクション</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>NotificationService#markAsRead（ONL-019）</t>
+          <t>呼出し元 Service のトランザクションに参加（読取は Spring Data 既定の readOnly）</t>
         </is>
       </c>
       <c r="C67" s="8" t="n"/>
@@ -11098,15 +10808,17 @@
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="9" t="n"/>
     </row>
-    <row r="68" ht="19" customHeight="1">
+    <row r="68" ht="49" customHeight="1">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>関連 ONL</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>ONL-019 通知一覧取得（API-019）</t>
+          <t>処理詳細（疑似コード）</t>
+        </is>
+      </c>
+      <c r="B68" s="15" t="inlineStr">
+        <is>
+          <t>実装クラスは作らない。メソッド名（Top50 / OrderBy…Desc）から次の SQL が生成される。
+SELECT * FROM notifications WHERE user_id = ? ORDER BY created_at DESC, id DESC LIMIT 50
+（PostgreSQL では FETCH FIRST 50 ROWS ONLY / LIMIT 形式）</t>
         </is>
       </c>
       <c r="C68" s="8" t="n"/>
@@ -11117,12 +10829,12 @@
     <row r="69" ht="19" customHeight="1">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>呼出先</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>主キー検索のため高速。id だけで検索してから userId を比較する実装にしない（WHERE 句で一括して判定する）。</t>
+          <t>（DB: notifications）</t>
         </is>
       </c>
       <c r="C69" s="8" t="n"/>
@@ -11131,12 +10843,16 @@
       <c r="F69" s="9" t="n"/>
     </row>
     <row r="70" ht="19" customHeight="1">
-      <c r="A70" s="14" t="inlineStr">
-        <is>
-          <t>③-2-3  NotificationRepository#existsByUserIdAndTypeAndCreatedAtGreaterThanEqualAndCreatedAtLessThan  （一覧 No. 3）</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="n"/>
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>呼出元</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>NotificationService#getNotifications（ONL-019）</t>
+        </is>
+      </c>
       <c r="C70" s="8" t="n"/>
       <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="n"/>
@@ -11145,12 +10861,12 @@
     <row r="71" ht="19" customHeight="1">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>種別</t>
+          <t>関連 ONL</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Repository（Spring Data JPA・本処理で追加）</t>
+          <t>ONL-019 通知一覧取得（API-019）</t>
         </is>
       </c>
       <c r="C71" s="8" t="n"/>
@@ -11158,15 +10874,16 @@
       <c r="E71" s="8" t="n"/>
       <c r="F71" s="9" t="n"/>
     </row>
-    <row r="72" ht="34" customHeight="1">
+    <row r="72" ht="49" customHeight="1">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>シグネチャ</t>
-        </is>
-      </c>
-      <c r="B72" s="15" t="inlineStr">
-        <is>
-          <t>boolean existsByUserIdAndTypeAndCreatedAtGreaterThanEqualAndCreatedAtLessThan(Long userId, String type, LocalDateTime from, LocalDateTime to)</t>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>idx_notif_user (user_id, is_read) で user_id による絞り込みが効く。並び替えは絞り込み後の行（本人分のみ、年間数十件）で行うため性能上問題ない。
+id を第2ソートキーにして、created_at が同一でも順序を決定的にする。</t>
         </is>
       </c>
       <c r="C72" s="8" t="n"/>
@@ -11175,16 +10892,12 @@
       <c r="F72" s="9" t="n"/>
     </row>
     <row r="73" ht="19" customHeight="1">
-      <c r="A73" s="10" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>指定ユーザー・種別の通知が期間 [from, to) に存在するかを返す。</t>
-        </is>
-      </c>
+      <c r="A73" s="14" t="inlineStr">
+        <is>
+          <t>③-2-3  NotificationRepository#findByIdAndUserId  （一覧 No. 3）</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="n"/>
       <c r="C73" s="8" t="n"/>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
@@ -11193,12 +10906,12 @@
     <row r="74" ht="19" customHeight="1">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>アノテーション</t>
+          <t>種別</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>Repository（Spring Data JPA・本処理で追加）</t>
         </is>
       </c>
       <c r="C74" s="8" t="n"/>
@@ -11207,79 +10920,67 @@
       <c r="F74" s="9" t="n"/>
     </row>
     <row r="75" ht="19" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>引数名</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>シグネチャ</t>
+        </is>
+      </c>
+      <c r="B75" s="15" t="inlineStr">
+        <is>
+          <t>Optional&lt;Notification&gt; findByIdAndUserId(Long id, Long userId)</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="n"/>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
       <c r="F75" s="9" t="n"/>
     </row>
     <row r="76" ht="19" customHeight="1">
-      <c r="A76" s="4" t="inlineStr">
-        <is>
-          <t>userId</t>
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>通知先ユーザーID</t>
-        </is>
-      </c>
+          <t>通知ID とユーザーIDの両方が一致する通知を1件返す（所有確認を兼ねる）。</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="n"/>
       <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
       <c r="F76" s="9" t="n"/>
     </row>
     <row r="77" ht="19" customHeight="1">
-      <c r="A77" s="4" t="inlineStr">
-        <is>
-          <t>type</t>
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>アノテーション</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>通知種別</t>
-        </is>
-      </c>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="n"/>
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
       <c r="F77" s="9" t="n"/>
     </row>
     <row r="78" ht="19" customHeight="1">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>from</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>LocalDateTime</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>期間の開始（含む）</t>
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>引数名</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="D78" s="8" t="n"/>
@@ -11289,17 +10990,17 @@
     <row r="79" ht="19" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>LocalDateTime</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>期間の終了（含まない）</t>
+          <t>通知ID</t>
         </is>
       </c>
       <c r="D79" s="8" t="n"/>
@@ -11307,17 +11008,21 @@
       <c r="F79" s="9" t="n"/>
     </row>
     <row r="80" ht="19" customHeight="1">
-      <c r="A80" s="10" t="inlineStr">
-        <is>
-          <t>戻り値</t>
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>userId</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="C80" s="8" t="n"/>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>ログインユーザーID</t>
+        </is>
+      </c>
       <c r="D80" s="8" t="n"/>
       <c r="E80" s="8" t="n"/>
       <c r="F80" s="9" t="n"/>
@@ -11325,12 +11030,12 @@
     <row r="81" ht="19" customHeight="1">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>例外</t>
+          <t>戻り値</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>Optional&lt;Notification&gt;（存在しない／他人の通知は Optional.empty()）</t>
         </is>
       </c>
       <c r="C81" s="8" t="n"/>
@@ -11341,12 +11046,12 @@
     <row r="82" ht="19" customHeight="1">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>トランザクション</t>
+          <t>例外</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>呼出し元 Service のトランザクションに参加（読取は Spring Data 既定の readOnly）</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="C82" s="8" t="n"/>
@@ -11354,15 +11059,15 @@
       <c r="E82" s="8" t="n"/>
       <c r="F82" s="9" t="n"/>
     </row>
-    <row r="83" ht="34" customHeight="1">
+    <row r="83" ht="19" customHeight="1">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>処理詳細（疑似コード）</t>
-        </is>
-      </c>
-      <c r="B83" s="15" t="inlineStr">
-        <is>
-          <t>SELECT EXISTS (SELECT 1 FROM notifications WHERE user_id = ? AND type = ? AND created_at &gt;= ? AND created_at &lt; ?)   -- 実際は Hibernate が LIMIT 1 の SELECT を発行する</t>
+          <t>トランザクション</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>呼出し元 Service のトランザクションに参加（読取は Spring Data 既定の readOnly）</t>
         </is>
       </c>
       <c r="C83" s="8" t="n"/>
@@ -11370,15 +11075,15 @@
       <c r="E83" s="8" t="n"/>
       <c r="F83" s="9" t="n"/>
     </row>
-    <row r="84" ht="19" customHeight="1">
+    <row r="84" ht="34" customHeight="1">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>呼出先</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>（DB: notifications）</t>
+          <t>処理詳細（疑似コード）</t>
+        </is>
+      </c>
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>SELECT * FROM notifications WHERE id = ? AND user_id = ?</t>
         </is>
       </c>
       <c r="C84" s="8" t="n"/>
@@ -11389,12 +11094,12 @@
     <row r="85" ht="19" customHeight="1">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>呼出元</t>
+          <t>呼出先</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>NotificationService#existsMonthly（ONL-019）</t>
+          <t>（DB: notifications）</t>
         </is>
       </c>
       <c r="C85" s="8" t="n"/>
@@ -11405,12 +11110,12 @@
     <row r="86" ht="19" customHeight="1">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>関連 ONL</t>
+          <t>呼出元</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>ONL-019 通知一覧取得（API-019）</t>
+          <t>NotificationService#markAsRead（ONL-019）</t>
         </is>
       </c>
       <c r="C86" s="8" t="n"/>
@@ -11421,12 +11126,12 @@
     <row r="87" ht="19" customHeight="1">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>関連 ONL</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>idx_notif_user (user_id, is_read) で user_id による絞り込みが効く。本人分のみ（年間数十件）のため性能上問題ない。</t>
+          <t>ONL-019 通知一覧取得（API-019）</t>
         </is>
       </c>
       <c r="C87" s="8" t="n"/>
@@ -11435,42 +11140,42 @@
       <c r="F87" s="9" t="n"/>
     </row>
     <row r="88" ht="19" customHeight="1">
-      <c r="A88" s="14" t="inlineStr">
-        <is>
-          <t>③-2-4  NotificationRepository#existsByUserIdAndTypeAndMessageStartingWithAndCreatedAtGreaterThanEqualAndCreatedAtLessThan  （一覧 No. 4）</t>
-        </is>
-      </c>
-      <c r="B88" s="8" t="n"/>
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>主キー検索のため高速。id だけで検索してから userId を比較する実装にしない（WHERE 句で一括して判定する）。</t>
+        </is>
+      </c>
       <c r="C88" s="8" t="n"/>
       <c r="D88" s="8" t="n"/>
       <c r="E88" s="8" t="n"/>
       <c r="F88" s="9" t="n"/>
     </row>
     <row r="89" ht="19" customHeight="1">
-      <c r="A89" s="10" t="inlineStr">
-        <is>
-          <t>種別</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>Repository（Spring Data JPA・本処理で追加）</t>
-        </is>
-      </c>
+      <c r="A89" s="14" t="inlineStr">
+        <is>
+          <t>③-2-4  NotificationRepository#existsByUserIdAndTypeAndCreatedAtGreaterThanEqualAndCreatedAtLessThan  （一覧 No. 4）</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="n"/>
       <c r="C89" s="8" t="n"/>
       <c r="D89" s="8" t="n"/>
       <c r="E89" s="8" t="n"/>
       <c r="F89" s="9" t="n"/>
     </row>
-    <row r="90" ht="34" customHeight="1">
+    <row r="90" ht="19" customHeight="1">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>シグネチャ</t>
-        </is>
-      </c>
-      <c r="B90" s="15" t="inlineStr">
-        <is>
-          <t>boolean existsByUserIdAndTypeAndMessageStartingWithAndCreatedAtGreaterThanEqualAndCreatedAtLessThan( Long userId, String type, String messagePrefix, LocalDateTime from, LocalDateTime to)</t>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>Repository（Spring Data JPA・本処理で追加）</t>
         </is>
       </c>
       <c r="C90" s="8" t="n"/>
@@ -11478,15 +11183,15 @@
       <c r="E90" s="8" t="n"/>
       <c r="F90" s="9" t="n"/>
     </row>
-    <row r="91" ht="19" customHeight="1">
+    <row r="91" ht="34" customHeight="1">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>指定ユーザー・種別で本文が messagePrefix で始まる通知が期間 [from, to) に存在するかを返す。</t>
+          <t>シグネチャ</t>
+        </is>
+      </c>
+      <c r="B91" s="15" t="inlineStr">
+        <is>
+          <t>boolean existsByUserIdAndTypeAndCreatedAtGreaterThanEqualAndCreatedAtLessThan(Long userId, String type, LocalDateTime from, LocalDateTime to)</t>
         </is>
       </c>
       <c r="C91" s="8" t="n"/>
@@ -11497,12 +11202,12 @@
     <row r="92" ht="19" customHeight="1">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>アノテーション</t>
+          <t>説明</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>指定ユーザー・種別の通知が期間 [from, to) に存在するかを返す。</t>
         </is>
       </c>
       <c r="C92" s="8" t="n"/>
@@ -11511,39 +11216,35 @@
       <c r="F92" s="9" t="n"/>
     </row>
     <row r="93" ht="19" customHeight="1">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>引数名</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
+      <c r="A93" s="10" t="inlineStr">
+        <is>
+          <t>アノテーション</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="n"/>
       <c r="D93" s="8" t="n"/>
       <c r="E93" s="8" t="n"/>
       <c r="F93" s="9" t="n"/>
     </row>
     <row r="94" ht="19" customHeight="1">
-      <c r="A94" s="4" t="inlineStr">
-        <is>
-          <t>userId</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="C94" s="4" t="inlineStr">
-        <is>
-          <t>通知先ユーザーID</t>
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>引数名</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="D94" s="8" t="n"/>
@@ -11553,17 +11254,17 @@
     <row r="95" ht="19" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>userId</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>通知種別</t>
+          <t>通知先ユーザーID</t>
         </is>
       </c>
       <c r="D95" s="8" t="n"/>
@@ -11573,7 +11274,7 @@
     <row r="96" ht="19" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>messagePrefix</t>
+          <t>type</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
@@ -11583,7 +11284,7 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>本文の前方一致キー</t>
+          <t>通知種別</t>
         </is>
       </c>
       <c r="D96" s="8" t="n"/>
@@ -11686,7 +11387,7 @@
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>SELECT 1 FROM notifications WHERE user_id = ? AND type = ? AND message LIKE ? ESCAPE '\' AND created_at &gt;= ? AND created_at &lt; ? LIMIT 1   -- 実際は Hibernate が発行（% _ \ はエスケープ）</t>
+          <t>SELECT EXISTS (SELECT 1 FROM notifications WHERE user_id = ? AND type = ? AND created_at &gt;= ? AND created_at &lt; ?)   -- 実際は Hibernate が LIMIT 1 の SELECT を発行する</t>
         </is>
       </c>
       <c r="C102" s="8" t="n"/>
@@ -11750,7 +11451,7 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>3 引数版用の existsByUserIdAndTypeAndCreatedAtGreaterThanEqualAndCreatedAtLessThan とは別メソッド。</t>
+          <t>idx_notif_user (user_id, is_read) で user_id による絞り込みが効く。本人分のみ（年間数十件）のため性能上問題ない。</t>
         </is>
       </c>
       <c r="C106" s="8" t="n"/>
@@ -12038,17 +11739,15 @@
       <c r="E124" s="8" t="n"/>
       <c r="F124" s="9" t="n"/>
     </row>
-    <row r="125" ht="49" customHeight="1">
+    <row r="125" ht="34" customHeight="1">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>設計原則（このクラス種別）</t>
+          <t>トランザクション境界</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>・Spring Data JPA。独自クエリは @Query（パラメータバインドのみ。文字列連結禁止）。
-・更新系 @Modifying は flushAutomatically = true, clearAutomatically = true を指定する。
-・@Lock は必ずトランザクション内で使用する。</t>
+          <t>@Transactional(readOnly = true)（Service）  ← existsByUserIdAndTypeAndMessageStartingWithAndCreatedAtGreaterThanEqualAndCreatedAtLessThan</t>
         </is>
       </c>
       <c r="C125" s="8" t="n"/>
@@ -12056,22 +11755,28 @@
       <c r="E125" s="8" t="n"/>
       <c r="F125" s="9" t="n"/>
     </row>
-    <row r="127">
-      <c r="A127" s="7" t="inlineStr">
+    <row r="126" ht="49" customHeight="1">
+      <c r="A126" s="10" t="inlineStr">
+        <is>
+          <t>設計原則（このクラス種別）</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>・Spring Data JPA。独自クエリは @Query（パラメータバインドのみ。文字列連結禁止）。
+・更新系 @Modifying は flushAutomatically = true, clearAutomatically = true を指定する。
+・@Lock は必ずトランザクション内で使用する。</t>
+        </is>
+      </c>
+      <c r="C126" s="8" t="n"/>
+      <c r="D126" s="8" t="n"/>
+      <c r="E126" s="8" t="n"/>
+      <c r="F126" s="9" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="7" t="inlineStr">
         <is>
           <t>⑥ 単体テスト観点（関連 ONL の tests を引用）</t>
-        </is>
-      </c>
-      <c r="B127" s="8" t="n"/>
-      <c r="C127" s="8" t="n"/>
-      <c r="D127" s="8" t="n"/>
-      <c r="E127" s="8" t="n"/>
-      <c r="F127" s="9" t="n"/>
-    </row>
-    <row r="128" ht="19" customHeight="1">
-      <c r="A128" s="6" t="inlineStr">
-        <is>
-          <t>ONL-019: NotificationRepository（@DataJpaTest + PostgreSQL / Testcontainers）</t>
         </is>
       </c>
       <c r="B128" s="8" t="n"/>
@@ -12083,91 +11788,75 @@
     <row r="129" ht="19" customHeight="1">
       <c r="A129" s="6" t="inlineStr">
         <is>
+          <t>ONL-019: NotificationRepository（@DataJpaTest + PostgreSQL / Testcontainers）</t>
+        </is>
+      </c>
+      <c r="B129" s="8" t="n"/>
+      <c r="C129" s="8" t="n"/>
+      <c r="D129" s="8" t="n"/>
+      <c r="E129" s="8" t="n"/>
+      <c r="F129" s="9" t="n"/>
+    </row>
+    <row r="130" ht="19" customHeight="1">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B129" s="6" t="inlineStr">
+      <c r="B130" s="6" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="C129" s="6" t="inlineStr">
+      <c r="C130" s="6" t="inlineStr">
         <is>
           <t>観点・条件</t>
         </is>
       </c>
-      <c r="D129" s="9" t="n"/>
-      <c r="E129" s="6" t="inlineStr">
+      <c r="D130" s="9" t="n"/>
+      <c r="E130" s="6" t="inlineStr">
         <is>
           <t>期待結果</t>
         </is>
       </c>
-      <c r="F129" s="6" t="inlineStr">
+      <c r="F130" s="6" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="34" customHeight="1">
-      <c r="A130" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B130" s="4" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="C130" s="4" t="inlineStr">
-        <is>
-          <t>本人の通知3件・他人の通知2件</t>
-        </is>
-      </c>
-      <c r="D130" s="9" t="n"/>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>本人の3件だけが created_at 降順で返る</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t>user_id 条件</t>
         </is>
       </c>
     </row>
     <row r="131" ht="34" customHeight="1">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>境界</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>本人の通知51件</t>
+          <t>本人の通知3件・他人の通知2件</t>
         </is>
       </c>
       <c r="D131" s="9" t="n"/>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>50件だけ返り、最も古い1件は含まれない</t>
+          <t>本人の3件だけが created_at 降順で返る</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>Top50 の上限</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="19" customHeight="1">
+          <t>user_id 条件</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="34" customHeight="1">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
@@ -12177,49 +11866,53 @@
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>created_at が同一の2件</t>
+          <t>本人の通知51件</t>
         </is>
       </c>
       <c r="D132" s="9" t="n"/>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>id の大きい方が先</t>
+          <t>50件だけ返り、最も古い1件は含まれない</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>第2ソートキー</t>
+          <t>Top50 の上限</t>
         </is>
       </c>
     </row>
     <row r="133" ht="19" customHeight="1">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>境界</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>通知0件</t>
+          <t>created_at が同一の2件</t>
         </is>
       </c>
       <c r="D133" s="9" t="n"/>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>空リスト</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr"/>
-    </row>
-    <row r="134" ht="64" customHeight="1">
+          <t>id の大きい方が先</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>第2ソートキー</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="19" customHeight="1">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
@@ -12229,49 +11922,45 @@
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>markAsRead: 本人の未読通知</t>
+          <t>通知0件</t>
         </is>
       </c>
       <c r="D134" s="9" t="n"/>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>戻り値 1。is_read = TRUE、updated_at は更新前より新しい（DB トリガ）、created_at は不変</t>
+          <t>空リスト</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr"/>
     </row>
-    <row r="135" ht="34" customHeight="1">
+    <row r="135" ht="64" customHeight="1">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>異常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>markAsRead: 他人の通知の ID に自分の userId を指定</t>
+          <t>markAsRead: 本人の未読通知</t>
         </is>
       </c>
       <c r="D135" s="9" t="n"/>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>戻り値 0。行は更新されない</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>WHERE user_id の確認</t>
-        </is>
-      </c>
+          <t>戻り値 1。is_read = TRUE、updated_at は更新前より新しい（DB トリガ）、created_at は不変</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr"/>
     </row>
     <row r="136" ht="34" customHeight="1">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
@@ -12281,26 +11970,53 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>markAsRead: 既読の通知</t>
+          <t>markAsRead: 他人の通知の ID に自分の userId を指定</t>
         </is>
       </c>
       <c r="D136" s="9" t="n"/>
       <c r="E136" s="4" t="inlineStr">
         <is>
+          <t>戻り値 0。行は更新されない</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>WHERE user_id の確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="34" customHeight="1">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>markAsRead: 既読の通知</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="n"/>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
           <t>戻り値 0。updated_at は変わらない</t>
         </is>
       </c>
-      <c r="F136" s="4" t="inlineStr">
+      <c r="F137" s="4" t="inlineStr">
         <is>
           <t>is_read = FALSE 条件</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="130">
+  <mergeCells count="131">
     <mergeCell ref="B106:F106"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="C61:F61"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B81:F81"/>
     <mergeCell ref="B90:F90"/>
@@ -12309,51 +12025,55 @@
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B58:F58"/>
     <mergeCell ref="B52:F52"/>
     <mergeCell ref="C78:F78"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="C134:D134"/>
+    <mergeCell ref="B60:F60"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="B53:F53"/>
+    <mergeCell ref="C64:F64"/>
     <mergeCell ref="C79:F79"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A58:F58"/>
     <mergeCell ref="B108:F108"/>
+    <mergeCell ref="C63:F63"/>
     <mergeCell ref="B84:F84"/>
-    <mergeCell ref="C93:F93"/>
     <mergeCell ref="B118:F118"/>
     <mergeCell ref="B92:F92"/>
+    <mergeCell ref="A73:F73"/>
     <mergeCell ref="A107:F107"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B15:F15"/>
-    <mergeCell ref="A70:F70"/>
-    <mergeCell ref="B80:F80"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="A124:F124"/>
     <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B54:F54"/>
     <mergeCell ref="B125:F125"/>
     <mergeCell ref="B72:F72"/>
     <mergeCell ref="B121:F121"/>
     <mergeCell ref="B56:F56"/>
+    <mergeCell ref="B70:F70"/>
     <mergeCell ref="B105:F105"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="C96:F96"/>
     <mergeCell ref="B111:F111"/>
     <mergeCell ref="B120:F120"/>
+    <mergeCell ref="C137:D137"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B88:F88"/>
     <mergeCell ref="C98:F98"/>
     <mergeCell ref="B82:F82"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="B19:F19"/>
-    <mergeCell ref="A127:F127"/>
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="C132:D132"/>
     <mergeCell ref="A30:F30"/>
@@ -12362,23 +12082,19 @@
     <mergeCell ref="B68:F68"/>
     <mergeCell ref="B83:F83"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="A88:F88"/>
+    <mergeCell ref="B76:F76"/>
     <mergeCell ref="B85:F85"/>
-    <mergeCell ref="C76:F76"/>
     <mergeCell ref="B4:F4"/>
-    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="B126:F126"/>
+    <mergeCell ref="B75:F75"/>
     <mergeCell ref="B109:F109"/>
-    <mergeCell ref="B47:F47"/>
     <mergeCell ref="B62:F62"/>
-    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="B59:F59"/>
     <mergeCell ref="A26:F26"/>
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="C77:F77"/>
+    <mergeCell ref="A129:F129"/>
     <mergeCell ref="C133:D133"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="B13:F13"/>
-    <mergeCell ref="C129:D129"/>
-    <mergeCell ref="B73:F73"/>
     <mergeCell ref="C45:F45"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="B87:F87"/>
@@ -12387,28 +12103,34 @@
     <mergeCell ref="C113:F113"/>
     <mergeCell ref="C112:F112"/>
     <mergeCell ref="C94:F94"/>
+    <mergeCell ref="C47:F47"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="A39:F39"/>
     <mergeCell ref="C44:F44"/>
     <mergeCell ref="B65:F65"/>
+    <mergeCell ref="C80:F80"/>
     <mergeCell ref="C114:F114"/>
-    <mergeCell ref="B63:F63"/>
+    <mergeCell ref="C46:F46"/>
     <mergeCell ref="C131:D131"/>
     <mergeCell ref="C95:F95"/>
     <mergeCell ref="B50:F50"/>
-    <mergeCell ref="C60:F60"/>
     <mergeCell ref="B110:F110"/>
+    <mergeCell ref="C48:F48"/>
     <mergeCell ref="B91:F91"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="A128:F128"/>
     <mergeCell ref="B100:F100"/>
     <mergeCell ref="B66:F66"/>
+    <mergeCell ref="A89:F89"/>
     <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B93:F93"/>
     <mergeCell ref="B102:F102"/>
     <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B77:F77"/>
     <mergeCell ref="B86:F86"/>
     <mergeCell ref="B117:F117"/>
     <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B61:F61"/>
     <mergeCell ref="B101:F101"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B119:F119"/>
@@ -12419,12 +12141,8 @@
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B49:F49"/>
     <mergeCell ref="B55:F55"/>
-    <mergeCell ref="C75:F75"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B89:F89"/>
     <mergeCell ref="B104:F104"/>
     <mergeCell ref="B51:F51"/>
-    <mergeCell ref="C59:F59"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="C136:D136"/>
     <mergeCell ref="B41:F41"/>
@@ -12854,7 +12572,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>notifications（DDL は KF-DD-003 テーブル設計書／backend/schema.sql）</t>
+          <t>notifications（DDL は KF-DD-003 テーブル設計書／backend/src/main/resources/db/migration/V1__init_schema.sql。Flyway で管理）</t>
         </is>
       </c>
       <c r="C26" s="8" t="n"/>
